--- a/data/nzd0137/nzd0137.xlsx
+++ b/data/nzd0137/nzd0137.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O584"/>
+  <dimension ref="A1:O586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30138,6 +30138,108 @@
         <v>389.88</v>
       </c>
       <c r="O584" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="n">
+        <v>446.14</v>
+      </c>
+      <c r="C585" t="n">
+        <v>461.62</v>
+      </c>
+      <c r="D585" t="n">
+        <v>384.93</v>
+      </c>
+      <c r="E585" t="n">
+        <v>369.43</v>
+      </c>
+      <c r="F585" t="n">
+        <v>370.51</v>
+      </c>
+      <c r="G585" t="n">
+        <v>374.22</v>
+      </c>
+      <c r="H585" t="n">
+        <v>375.94</v>
+      </c>
+      <c r="I585" t="n">
+        <v>378.51</v>
+      </c>
+      <c r="J585" t="n">
+        <v>385.01</v>
+      </c>
+      <c r="K585" t="n">
+        <v>383.12</v>
+      </c>
+      <c r="L585" t="n">
+        <v>388.32</v>
+      </c>
+      <c r="M585" t="n">
+        <v>387.93</v>
+      </c>
+      <c r="N585" t="n">
+        <v>387.48</v>
+      </c>
+      <c r="O585" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="n">
+        <v>446.14</v>
+      </c>
+      <c r="C586" t="n">
+        <v>465.48</v>
+      </c>
+      <c r="D586" t="n">
+        <v>386.45</v>
+      </c>
+      <c r="E586" t="n">
+        <v>370.68</v>
+      </c>
+      <c r="F586" t="n">
+        <v>372.06</v>
+      </c>
+      <c r="G586" t="n">
+        <v>375.19</v>
+      </c>
+      <c r="H586" t="n">
+        <v>377.68</v>
+      </c>
+      <c r="I586" t="n">
+        <v>379.13</v>
+      </c>
+      <c r="J586" t="n">
+        <v>385.69</v>
+      </c>
+      <c r="K586" t="n">
+        <v>384.28</v>
+      </c>
+      <c r="L586" t="n">
+        <v>389.18</v>
+      </c>
+      <c r="M586" t="n">
+        <v>388.44</v>
+      </c>
+      <c r="N586" t="n">
+        <v>387.63</v>
+      </c>
+      <c r="O586" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -30154,7 +30256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B595"/>
+  <dimension ref="A1:B597"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36107,6 +36209,26 @@
       </c>
       <c r="B595" t="n">
         <v>0.68</v>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="n">
+        <v>1.38</v>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>1.4</v>
       </c>
     </row>
   </sheetData>
@@ -36275,28 +36397,28 @@
         <v>0.0117</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.01228386731568009</v>
+        <v>-0.02410071990353968</v>
       </c>
       <c r="J2" t="n">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="K2" t="n">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="L2" t="n">
-        <v>1.281656298501854e-05</v>
+        <v>4.96511120579024e-05</v>
       </c>
       <c r="M2" t="n">
-        <v>18.87034210254966</v>
+        <v>18.84983619932826</v>
       </c>
       <c r="N2" t="n">
-        <v>590.1161597946998</v>
+        <v>588.9231648446389</v>
       </c>
       <c r="O2" t="n">
-        <v>24.29230659683637</v>
+        <v>24.26773917868409</v>
       </c>
       <c r="P2" t="n">
-        <v>462.4120373499009</v>
+        <v>462.5425391802435</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -36357,28 +36479,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.17885409132376</v>
+        <v>-0.1713965995580701</v>
       </c>
       <c r="J3" t="n">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="K3" t="n">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0060346299927726</v>
+        <v>0.005581156735282478</v>
       </c>
       <c r="M3" t="n">
-        <v>12.61020399205324</v>
+        <v>12.60554247010269</v>
       </c>
       <c r="N3" t="n">
-        <v>262.2647622838569</v>
+        <v>261.7233280679233</v>
       </c>
       <c r="O3" t="n">
-        <v>16.19459052535311</v>
+        <v>16.1778653742675</v>
       </c>
       <c r="P3" t="n">
-        <v>458.164452562232</v>
+        <v>458.0824369583631</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -36439,28 +36561,28 @@
         <v>0.0257</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.02520127402459737</v>
+        <v>-0.03358413081979884</v>
       </c>
       <c r="J4" t="n">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="K4" t="n">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0003611478087385267</v>
+        <v>0.0006430577309445296</v>
       </c>
       <c r="M4" t="n">
-        <v>6.987401674294208</v>
+        <v>7.002554942027964</v>
       </c>
       <c r="N4" t="n">
-        <v>87.80705108553637</v>
+        <v>87.9468341066713</v>
       </c>
       <c r="O4" t="n">
-        <v>9.370541664468302</v>
+        <v>9.377997339873332</v>
       </c>
       <c r="P4" t="n">
-        <v>397.7231624352976</v>
+        <v>397.8153262795959</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -36521,28 +36643,28 @@
         <v>0.0308</v>
       </c>
       <c r="I5" t="n">
-        <v>0.003609570873972511</v>
+        <v>-0.003458303001485452</v>
       </c>
       <c r="J5" t="n">
+        <v>585</v>
+      </c>
+      <c r="K5" t="n">
         <v>583</v>
       </c>
-      <c r="K5" t="n">
-        <v>581</v>
-      </c>
       <c r="L5" t="n">
-        <v>1.509346387307264e-05</v>
+        <v>1.386321416507741e-05</v>
       </c>
       <c r="M5" t="n">
-        <v>4.666865697452933</v>
+        <v>4.686667120912387</v>
       </c>
       <c r="N5" t="n">
-        <v>43.56458166805209</v>
+        <v>43.73460831030933</v>
       </c>
       <c r="O5" t="n">
-        <v>6.600347086938086</v>
+        <v>6.613214672933982</v>
       </c>
       <c r="P5" t="n">
-        <v>379.64384132606</v>
+        <v>379.7209234953551</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -36603,28 +36725,28 @@
         <v>0.0327</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1035787786839977</v>
+        <v>-0.107300430345035</v>
       </c>
       <c r="J6" t="n">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="K6" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0232394888531765</v>
+        <v>0.02499469000077514</v>
       </c>
       <c r="M6" t="n">
-        <v>3.595063784182347</v>
+        <v>3.600007699420416</v>
       </c>
       <c r="N6" t="n">
-        <v>22.5372803298418</v>
+        <v>22.54911601345876</v>
       </c>
       <c r="O6" t="n">
-        <v>4.747344555627051</v>
+        <v>4.748590950319763</v>
       </c>
       <c r="P6" t="n">
-        <v>379.0891079079633</v>
+        <v>379.1299051978322</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -36685,28 +36807,28 @@
         <v>0.0372</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03430441036185161</v>
+        <v>-0.03832491894229264</v>
       </c>
       <c r="J7" t="n">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="K7" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003129734174776355</v>
+        <v>0.003913038660973811</v>
       </c>
       <c r="M7" t="n">
-        <v>3.370295948073223</v>
+        <v>3.380860359786917</v>
       </c>
       <c r="N7" t="n">
-        <v>18.73395708520088</v>
+        <v>18.77210495842898</v>
       </c>
       <c r="O7" t="n">
-        <v>4.328274146262096</v>
+        <v>4.332678727811349</v>
       </c>
       <c r="P7" t="n">
-        <v>381.0879296791009</v>
+        <v>381.1320032346403</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -36767,28 +36889,28 @@
         <v>0.0354</v>
       </c>
       <c r="I8" t="n">
-        <v>0.006195852516051111</v>
+        <v>0.005263851110539481</v>
       </c>
       <c r="J8" t="n">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="K8" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001785951148002285</v>
+        <v>0.0001298462150267632</v>
       </c>
       <c r="M8" t="n">
-        <v>2.458284987917799</v>
+        <v>2.453783928261037</v>
       </c>
       <c r="N8" t="n">
-        <v>10.74121503057636</v>
+        <v>10.71245155207122</v>
       </c>
       <c r="O8" t="n">
-        <v>3.277379293059679</v>
+        <v>3.272988168642109</v>
       </c>
       <c r="P8" t="n">
-        <v>377.9151076046099</v>
+        <v>377.9253240476482</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -36849,28 +36971,28 @@
         <v>0.0516</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08018848187366365</v>
+        <v>0.079540745785321</v>
       </c>
       <c r="J9" t="n">
+        <v>585</v>
+      </c>
+      <c r="K9" t="n">
         <v>583</v>
       </c>
-      <c r="K9" t="n">
-        <v>581</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.03264778994181783</v>
+        <v>0.03237809034113059</v>
       </c>
       <c r="M9" t="n">
-        <v>2.319790234607268</v>
+        <v>2.314746089770301</v>
       </c>
       <c r="N9" t="n">
-        <v>9.536121022610283</v>
+        <v>9.506373795567139</v>
       </c>
       <c r="O9" t="n">
-        <v>3.088061045803707</v>
+        <v>3.083240794288883</v>
       </c>
       <c r="P9" t="n">
-        <v>377.5864735963189</v>
+        <v>377.5935716911039</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -36931,28 +37053,28 @@
         <v>0.0608</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0006905548372810816</v>
+        <v>-0.0006547296959578443</v>
       </c>
       <c r="J10" t="n">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="K10" t="n">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="L10" t="n">
-        <v>2.643642094790621e-06</v>
+        <v>2.392288531272158e-06</v>
       </c>
       <c r="M10" t="n">
-        <v>2.233717445378923</v>
+        <v>2.231845425655128</v>
       </c>
       <c r="N10" t="n">
-        <v>9.054482368197155</v>
+        <v>9.035146818650366</v>
       </c>
       <c r="O10" t="n">
-        <v>3.009066693876551</v>
+        <v>3.005852095271882</v>
       </c>
       <c r="P10" t="n">
-        <v>387.1630439146715</v>
+        <v>387.1777755943943</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -37013,28 +37135,28 @@
         <v>0.0586</v>
       </c>
       <c r="I11" t="n">
-        <v>0.004777078885016436</v>
+        <v>0.001240077280354288</v>
       </c>
       <c r="J11" t="n">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="K11" t="n">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0001050416761063655</v>
+        <v>7.083288002251997e-06</v>
       </c>
       <c r="M11" t="n">
-        <v>2.455498488794319</v>
+        <v>2.460251933132679</v>
       </c>
       <c r="N11" t="n">
-        <v>10.9040705307274</v>
+        <v>10.94675146377517</v>
       </c>
       <c r="O11" t="n">
-        <v>3.302131210404487</v>
+        <v>3.308587533038104</v>
       </c>
       <c r="P11" t="n">
-        <v>388.3934674629764</v>
+        <v>388.4321999070422</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -37095,28 +37217,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.0255020483569339</v>
+        <v>0.02132636982561347</v>
       </c>
       <c r="J12" t="n">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="K12" t="n">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="L12" t="n">
-        <v>0.002755356588523883</v>
+        <v>0.001925781893387213</v>
       </c>
       <c r="M12" t="n">
-        <v>2.554329722987373</v>
+        <v>2.562498268219558</v>
       </c>
       <c r="N12" t="n">
-        <v>11.81531000302702</v>
+        <v>11.88544217001055</v>
       </c>
       <c r="O12" t="n">
-        <v>3.437340542196397</v>
+        <v>3.447526964363085</v>
       </c>
       <c r="P12" t="n">
-        <v>393.7696070499629</v>
+        <v>393.8153335306735</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -37177,28 +37299,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.07943751438975465</v>
+        <v>0.07704735895632063</v>
       </c>
       <c r="J13" t="n">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="K13" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02598621490564035</v>
+        <v>0.02460110968668727</v>
       </c>
       <c r="M13" t="n">
-        <v>2.476413953394873</v>
+        <v>2.478562355294945</v>
       </c>
       <c r="N13" t="n">
-        <v>11.82147815307282</v>
+        <v>11.81708719502686</v>
       </c>
       <c r="O13" t="n">
-        <v>3.438237652209752</v>
+        <v>3.437599045122461</v>
       </c>
       <c r="P13" t="n">
-        <v>389.3447898435843</v>
+        <v>389.370991182417</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -37259,28 +37381,28 @@
         <v>0.1502</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0496564105603338</v>
+        <v>0.05013316787977676</v>
       </c>
       <c r="J14" t="n">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="K14" t="n">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01040911098231989</v>
+        <v>0.01069035756586256</v>
       </c>
       <c r="M14" t="n">
-        <v>2.705949161939217</v>
+        <v>2.699104606627871</v>
       </c>
       <c r="N14" t="n">
-        <v>11.70632580504861</v>
+        <v>11.66754394619633</v>
       </c>
       <c r="O14" t="n">
-        <v>3.421450833352514</v>
+        <v>3.415778673479346</v>
       </c>
       <c r="P14" t="n">
-        <v>385.5968577562441</v>
+        <v>385.5916221172856</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -37322,7 +37444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O584"/>
+  <dimension ref="A1:O586"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82097,6 +82219,160 @@
         </is>
       </c>
     </row>
+    <row r="585">
+      <c r="A585" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-07 22:12:09+00:00</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>-36.56201943044017,174.69785066878205</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>-36.56275399923067,174.69774812276407</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>-36.563227826413666,174.69663642468788</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>-36.56387898836577,174.69620139389974</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>-36.564535484034735,174.69581164685516</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>-36.56517877284109,174.69543192101392</t>
+        </is>
+      </c>
+      <c r="H585" t="inlineStr">
+        <is>
+          <t>-36.565856663520904,174.69518660557662</t>
+        </is>
+      </c>
+      <c r="I585" t="inlineStr">
+        <is>
+          <t>-36.56655086028807,174.69497434394276</t>
+        </is>
+      </c>
+      <c r="J585" t="inlineStr">
+        <is>
+          <t>-36.56724125590735,174.69485882814146</t>
+        </is>
+      </c>
+      <c r="K585" t="inlineStr">
+        <is>
+          <t>-36.567942991023415,174.6947967980063</t>
+        </is>
+      </c>
+      <c r="L585" t="inlineStr">
+        <is>
+          <t>-36.568654461472875,174.69481271828155</t>
+        </is>
+      </c>
+      <c r="M585" t="inlineStr">
+        <is>
+          <t>-36.569341753956664,174.69484106129812</t>
+        </is>
+      </c>
+      <c r="N585" t="inlineStr">
+        <is>
+          <t>-36.57001597735589,174.69501893527217</t>
+        </is>
+      </c>
+      <c r="O585" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="inlineStr">
+        <is>
+          <t>2025-12-08 22:06:18+00:00</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>-36.56201943044017,174.69785066878205</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>-36.5627644711536,174.69778924703232</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>-36.56323196550335,174.69665261275458</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>-36.56388305929818,174.69621441560193</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>-36.56454170705342,174.69582715087193</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>-36.56518204657558,174.6954419697697</t>
+        </is>
+      </c>
+      <c r="H586" t="inlineStr">
+        <is>
+          <t>-36.56586094015121,174.69520530901187</t>
+        </is>
+      </c>
+      <c r="I586" t="inlineStr">
+        <is>
+          <t>-36.56655214417406,174.69498108568314</t>
+        </is>
+      </c>
+      <c r="J586" t="inlineStr">
+        <is>
+          <t>-36.56724198302833,174.69486637197718</t>
+        </is>
+      </c>
+      <c r="K586" t="inlineStr">
+        <is>
+          <t>-36.56794335959998,174.69480975050672</t>
+        </is>
+      </c>
+      <c r="L586" t="inlineStr">
+        <is>
+          <t>-36.5686543971188,174.69482232672758</t>
+        </is>
+      </c>
+      <c r="M586" t="inlineStr">
+        <is>
+          <t>-36.569341121454,174.69484670536744</t>
+        </is>
+      </c>
+      <c r="N586" t="inlineStr">
+        <is>
+          <t>-36.57001567545551,174.69502056892483</t>
+        </is>
+      </c>
+      <c r="O586" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0137/nzd0137.xlsx
+++ b/data/nzd0137/nzd0137.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O586"/>
+  <dimension ref="A1:O588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30240,6 +30240,108 @@
         <v>387.63</v>
       </c>
       <c r="O586" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="n">
+        <v>446.14</v>
+      </c>
+      <c r="C587" t="n">
+        <v>469.6</v>
+      </c>
+      <c r="D587" t="n">
+        <v>388.84</v>
+      </c>
+      <c r="E587" t="n">
+        <v>369.65</v>
+      </c>
+      <c r="F587" t="n">
+        <v>371.5</v>
+      </c>
+      <c r="G587" t="n">
+        <v>378.65</v>
+      </c>
+      <c r="H587" t="n">
+        <v>378.3</v>
+      </c>
+      <c r="I587" t="n">
+        <v>379.59</v>
+      </c>
+      <c r="J587" t="n">
+        <v>386.23</v>
+      </c>
+      <c r="K587" t="n">
+        <v>385.93</v>
+      </c>
+      <c r="L587" t="n">
+        <v>390.35</v>
+      </c>
+      <c r="M587" t="n">
+        <v>389.39</v>
+      </c>
+      <c r="N587" t="n">
+        <v>383.49</v>
+      </c>
+      <c r="O587" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="n">
+        <v>443.79</v>
+      </c>
+      <c r="C588" t="n">
+        <v>469.6</v>
+      </c>
+      <c r="D588" t="n">
+        <v>388.84</v>
+      </c>
+      <c r="E588" t="n">
+        <v>369.65</v>
+      </c>
+      <c r="F588" t="n">
+        <v>371.5</v>
+      </c>
+      <c r="G588" t="n">
+        <v>378.65</v>
+      </c>
+      <c r="H588" t="n">
+        <v>378.3</v>
+      </c>
+      <c r="I588" t="n">
+        <v>379.59</v>
+      </c>
+      <c r="J588" t="n">
+        <v>389.14</v>
+      </c>
+      <c r="K588" t="n">
+        <v>385.93</v>
+      </c>
+      <c r="L588" t="n">
+        <v>390.62</v>
+      </c>
+      <c r="M588" t="n">
+        <v>389.39</v>
+      </c>
+      <c r="N588" t="n">
+        <v>383.49</v>
+      </c>
+      <c r="O588" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -30256,7 +30358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B597"/>
+  <dimension ref="A1:B600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36229,6 +36331,36 @@
       </c>
       <c r="B597" t="n">
         <v>1.4</v>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>2025-12-24 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="n">
+        <v>1.06</v>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="n">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="n">
+        <v>0.54</v>
       </c>
     </row>
   </sheetData>
@@ -36397,28 +36529,28 @@
         <v>0.0117</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02410071990353968</v>
+        <v>-0.03660526474867733</v>
       </c>
       <c r="J2" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K2" t="n">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="L2" t="n">
-        <v>4.96511120579024e-05</v>
+        <v>0.0001152454134956127</v>
       </c>
       <c r="M2" t="n">
-        <v>18.84983619932826</v>
+        <v>18.83213109101065</v>
       </c>
       <c r="N2" t="n">
-        <v>588.9231648446389</v>
+        <v>587.8570146572762</v>
       </c>
       <c r="O2" t="n">
-        <v>24.26773917868409</v>
+        <v>24.24576281863031</v>
       </c>
       <c r="P2" t="n">
-        <v>462.5425391802435</v>
+        <v>462.6810741661159</v>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
@@ -36479,28 +36611,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1713965995580701</v>
+        <v>-0.1596007365602315</v>
       </c>
       <c r="J3" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K3" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L3" t="n">
-        <v>0.005581156735282478</v>
+        <v>0.004865379969694605</v>
       </c>
       <c r="M3" t="n">
-        <v>12.60554247010269</v>
+        <v>12.62314965863472</v>
       </c>
       <c r="N3" t="n">
-        <v>261.7233280679233</v>
+        <v>261.6995255729336</v>
       </c>
       <c r="O3" t="n">
-        <v>16.1778653742675</v>
+        <v>16.17712970748932</v>
       </c>
       <c r="P3" t="n">
-        <v>458.0824369583631</v>
+        <v>457.9523140199366</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
@@ -36561,28 +36693,28 @@
         <v>0.0257</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03358413081979884</v>
+        <v>-0.03952255991197137</v>
       </c>
       <c r="J4" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K4" t="n">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0006430577309445296</v>
+        <v>0.0008951958886490585</v>
       </c>
       <c r="M4" t="n">
-        <v>7.002554942027964</v>
+        <v>7.006227560467445</v>
       </c>
       <c r="N4" t="n">
-        <v>87.9468341066713</v>
+        <v>87.8665204620112</v>
       </c>
       <c r="O4" t="n">
-        <v>9.377997339873332</v>
+        <v>9.373714336484294</v>
       </c>
       <c r="P4" t="n">
-        <v>397.8153262795959</v>
+        <v>397.8808165965615</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -36643,28 +36775,28 @@
         <v>0.0308</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.003458303001485452</v>
+        <v>-0.01070818513145323</v>
       </c>
       <c r="J5" t="n">
+        <v>587</v>
+      </c>
+      <c r="K5" t="n">
         <v>585</v>
       </c>
-      <c r="K5" t="n">
-        <v>583</v>
-      </c>
       <c r="L5" t="n">
-        <v>1.386321416507741e-05</v>
+        <v>0.000132929587161712</v>
       </c>
       <c r="M5" t="n">
-        <v>4.686667120912387</v>
+        <v>4.707460289072598</v>
       </c>
       <c r="N5" t="n">
-        <v>43.73460831030933</v>
+        <v>43.92143651710362</v>
       </c>
       <c r="O5" t="n">
-        <v>6.613214672933982</v>
+        <v>6.627324989549224</v>
       </c>
       <c r="P5" t="n">
-        <v>379.7209234953551</v>
+        <v>379.8002357151233</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
@@ -36725,28 +36857,28 @@
         <v>0.0327</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.107300430345035</v>
+        <v>-0.1108012044116833</v>
       </c>
       <c r="J6" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K6" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02499469000077514</v>
+        <v>0.0267256155576997</v>
       </c>
       <c r="M6" t="n">
-        <v>3.600007699420416</v>
+        <v>3.603818791689439</v>
       </c>
       <c r="N6" t="n">
-        <v>22.54911601345876</v>
+        <v>22.54948789250881</v>
       </c>
       <c r="O6" t="n">
-        <v>4.748590950319763</v>
+        <v>4.748630106937032</v>
       </c>
       <c r="P6" t="n">
-        <v>379.1299051978322</v>
+        <v>379.1683989904149</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -36807,28 +36939,28 @@
         <v>0.0372</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03832491894229264</v>
+        <v>-0.03939750130782981</v>
       </c>
       <c r="J7" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K7" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L7" t="n">
-        <v>0.003913038660973811</v>
+        <v>0.004165508035954946</v>
       </c>
       <c r="M7" t="n">
-        <v>3.380860359786917</v>
+        <v>3.375267083033719</v>
       </c>
       <c r="N7" t="n">
-        <v>18.77210495842898</v>
+        <v>18.71529553818372</v>
       </c>
       <c r="O7" t="n">
-        <v>4.332678727811349</v>
+        <v>4.326117836835206</v>
       </c>
       <c r="P7" t="n">
-        <v>381.1320032346403</v>
+        <v>381.1437971298184</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
@@ -36889,28 +37021,28 @@
         <v>0.0354</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005263851110539481</v>
+        <v>0.005438999720699897</v>
       </c>
       <c r="J8" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K8" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0001298462150267632</v>
+        <v>0.0001397351130922875</v>
       </c>
       <c r="M8" t="n">
-        <v>2.453783928261037</v>
+        <v>2.44629088494472</v>
       </c>
       <c r="N8" t="n">
-        <v>10.71245155207122</v>
+        <v>10.67608385512945</v>
       </c>
       <c r="O8" t="n">
-        <v>3.272988168642109</v>
+        <v>3.267427712303587</v>
       </c>
       <c r="P8" t="n">
-        <v>377.9253240476482</v>
+        <v>377.9233981495021</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -36971,28 +37103,28 @@
         <v>0.0516</v>
       </c>
       <c r="I9" t="n">
-        <v>0.079540745785321</v>
+        <v>0.07945774163440569</v>
       </c>
       <c r="J9" t="n">
+        <v>587</v>
+      </c>
+      <c r="K9" t="n">
         <v>585</v>
       </c>
-      <c r="K9" t="n">
-        <v>583</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.03237809034113059</v>
+        <v>0.03256229426371859</v>
       </c>
       <c r="M9" t="n">
-        <v>2.314746089770301</v>
+        <v>2.307202673743596</v>
       </c>
       <c r="N9" t="n">
-        <v>9.506373795567139</v>
+        <v>9.473916936989186</v>
       </c>
       <c r="O9" t="n">
-        <v>3.083240794288883</v>
+        <v>3.077972861639489</v>
       </c>
       <c r="P9" t="n">
-        <v>377.5935716911039</v>
+        <v>377.5944840889538</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
@@ -37053,28 +37185,28 @@
         <v>0.0608</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0006547296959578443</v>
+        <v>-0.0002708172673536895</v>
       </c>
       <c r="J10" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K10" t="n">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L10" t="n">
-        <v>2.392288531272158e-06</v>
+        <v>4.121918127930613e-07</v>
       </c>
       <c r="M10" t="n">
-        <v>2.231845425655128</v>
+        <v>2.229316765553964</v>
       </c>
       <c r="N10" t="n">
-        <v>9.035146818650366</v>
+        <v>9.012336853560379</v>
       </c>
       <c r="O10" t="n">
-        <v>3.005852095271882</v>
+        <v>3.002055438122417</v>
       </c>
       <c r="P10" t="n">
-        <v>387.1777755943943</v>
+        <v>387.1735534406368</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
@@ -37135,28 +37267,28 @@
         <v>0.0586</v>
       </c>
       <c r="I11" t="n">
-        <v>0.001240077280354288</v>
+        <v>-0.0006133756688680062</v>
       </c>
       <c r="J11" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K11" t="n">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L11" t="n">
-        <v>7.083288002251997e-06</v>
+        <v>1.743316888958013e-06</v>
       </c>
       <c r="M11" t="n">
-        <v>2.460251933132679</v>
+        <v>2.458668087850325</v>
       </c>
       <c r="N11" t="n">
-        <v>10.94675146377517</v>
+        <v>10.93100889367629</v>
       </c>
       <c r="O11" t="n">
-        <v>3.308587533038104</v>
+        <v>3.306207630152148</v>
       </c>
       <c r="P11" t="n">
-        <v>388.4321999070422</v>
+        <v>388.4525591848005</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
@@ -37217,28 +37349,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.02132636982561347</v>
+        <v>0.01847796496669135</v>
       </c>
       <c r="J12" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K12" t="n">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001925781893387213</v>
+        <v>0.001451615685494456</v>
       </c>
       <c r="M12" t="n">
-        <v>2.562498268219558</v>
+        <v>2.565794132888296</v>
       </c>
       <c r="N12" t="n">
-        <v>11.88544217001055</v>
+        <v>11.896247551181</v>
       </c>
       <c r="O12" t="n">
-        <v>3.447526964363085</v>
+        <v>3.44909372896432</v>
       </c>
       <c r="P12" t="n">
-        <v>393.8153335306735</v>
+        <v>393.8466213981096</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
@@ -37299,28 +37431,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.07704735895632063</v>
+        <v>0.07557188238839149</v>
       </c>
       <c r="J13" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K13" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02460110968668727</v>
+        <v>0.02384768651548319</v>
       </c>
       <c r="M13" t="n">
-        <v>2.478562355294945</v>
+        <v>2.476615545159184</v>
       </c>
       <c r="N13" t="n">
-        <v>11.81708719502686</v>
+        <v>11.79049282203377</v>
       </c>
       <c r="O13" t="n">
-        <v>3.437599045122461</v>
+        <v>3.433728705362986</v>
       </c>
       <c r="P13" t="n">
-        <v>389.370991182417</v>
+        <v>389.3872152243285</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
@@ -37381,28 +37513,28 @@
         <v>0.1502</v>
       </c>
       <c r="I14" t="n">
-        <v>0.05013316787977676</v>
+        <v>0.04762475163841496</v>
       </c>
       <c r="J14" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="K14" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L14" t="n">
-        <v>0.01069035756586256</v>
+        <v>0.009700995824704961</v>
       </c>
       <c r="M14" t="n">
-        <v>2.699104606627871</v>
+        <v>2.700286521161926</v>
       </c>
       <c r="N14" t="n">
-        <v>11.66754394619633</v>
+        <v>11.66728379189156</v>
       </c>
       <c r="O14" t="n">
-        <v>3.415778673479346</v>
+        <v>3.415740592008058</v>
       </c>
       <c r="P14" t="n">
-        <v>385.5916221172856</v>
+        <v>385.6192533284306</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
@@ -37444,7 +37576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O586"/>
+  <dimension ref="A1:O588"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82373,6 +82505,160 @@
         </is>
       </c>
     </row>
+    <row r="587">
+      <c r="A587" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>-36.56201943044017,174.69785066878205</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>-36.56277564842323,174.69783314134068</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>-36.56323847367275,174.69667806636278</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>-36.56387970484999,174.6962036857192</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>-36.56453945873723,174.69582154942043</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>-36.56519372401314,174.69547781379174</t>
+        </is>
+      </c>
+      <c r="H587" t="inlineStr">
+        <is>
+          <t>-36.56586246400725,174.69521197345478</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr">
+        <is>
+          <t>-36.566553096734395,174.6949860876197</t>
+        </is>
+      </c>
+      <c r="J587" t="inlineStr">
+        <is>
+          <t>-36.56724256044757,174.6948723626704</t>
+        </is>
+      </c>
+      <c r="K587" t="inlineStr">
+        <is>
+          <t>-36.56794388386594,174.69482817432208</t>
+        </is>
+      </c>
+      <c r="L587" t="inlineStr">
+        <is>
+          <t>-36.56865430956607,174.69483539868313</t>
+        </is>
+      </c>
+      <c r="M587" t="inlineStr">
+        <is>
+          <t>-36.569339943262044,174.69485721882958</t>
+        </is>
+      </c>
+      <c r="N587" t="inlineStr">
+        <is>
+          <t>-36.5700240078978,174.69497548010636</t>
+        </is>
+      </c>
+      <c r="O587" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>-36.56201339099504,174.6978255045612</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>-36.56277564842323,174.69783314134068</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>-36.56323847367275,174.69667806636278</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>-36.56387970484999,174.6962036857192</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>-36.56453945873723,174.69582154942043</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>-36.56519372401314,174.69547781379174</t>
+        </is>
+      </c>
+      <c r="H588" t="inlineStr">
+        <is>
+          <t>-36.56586246400725,174.69521197345478</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr">
+        <is>
+          <t>-36.566553096734395,174.6949860876197</t>
+        </is>
+      </c>
+      <c r="J588" t="inlineStr">
+        <is>
+          <t>-36.56724567209054,174.69490464585164</t>
+        </is>
+      </c>
+      <c r="K588" t="inlineStr">
+        <is>
+          <t>-36.56794388386594,174.69482817432208</t>
+        </is>
+      </c>
+      <c r="L588" t="inlineStr">
+        <is>
+          <t>-36.56865428936139,174.69483841528825</t>
+        </is>
+      </c>
+      <c r="M588" t="inlineStr">
+        <is>
+          <t>-36.569339943262044,174.69485721882958</t>
+        </is>
+      </c>
+      <c r="N588" t="inlineStr">
+        <is>
+          <t>-36.5700240078978,174.69497548010636</t>
+        </is>
+      </c>
+      <c r="O588" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0137/nzd0137.xlsx
+++ b/data/nzd0137/nzd0137.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O588"/>
+  <dimension ref="A1:O589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30342,6 +30342,57 @@
         <v>383.49</v>
       </c>
       <c r="O588" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="n">
+        <v>432.56</v>
+      </c>
+      <c r="C589" t="n">
+        <v>471.92</v>
+      </c>
+      <c r="D589" t="n">
+        <v>391.31</v>
+      </c>
+      <c r="E589" t="n">
+        <v>369.55</v>
+      </c>
+      <c r="F589" t="n">
+        <v>372.23</v>
+      </c>
+      <c r="G589" t="n">
+        <v>379.68</v>
+      </c>
+      <c r="H589" t="n">
+        <v>380.08</v>
+      </c>
+      <c r="I589" t="n">
+        <v>381.26</v>
+      </c>
+      <c r="J589" t="n">
+        <v>391.56</v>
+      </c>
+      <c r="K589" t="n">
+        <v>385.3</v>
+      </c>
+      <c r="L589" t="n">
+        <v>391.67</v>
+      </c>
+      <c r="M589" t="n">
+        <v>387.16</v>
+      </c>
+      <c r="N589" t="n">
+        <v>382.12</v>
+      </c>
+      <c r="O589" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -30358,7 +30409,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B600"/>
+  <dimension ref="A1:B601"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36361,6 +36412,16 @@
       </c>
       <c r="B600" t="n">
         <v>0.54</v>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>-0.21</v>
       </c>
     </row>
   </sheetData>
@@ -36529,34 +36590,30 @@
         <v>0.0117</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03660526474867733</v>
+        <v>-0.04740220468846788</v>
       </c>
       <c r="J2" t="n">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="K2" t="n">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001152454134956127</v>
+        <v>0.0001935245630778626</v>
       </c>
       <c r="M2" t="n">
-        <v>18.83213109101065</v>
+        <v>18.84094234317247</v>
       </c>
       <c r="N2" t="n">
-        <v>587.8570146572762</v>
+        <v>588.3073682568007</v>
       </c>
       <c r="O2" t="n">
-        <v>24.24576281863031</v>
+        <v>24.2550483045654</v>
       </c>
       <c r="P2" t="n">
-        <v>462.6810741661159</v>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>462.8011584833621</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>LINESTRING (174.69307338857172 -36.56087276386966, 174.70294077624177 -36.563240932878394)</t>
@@ -36611,34 +36668,30 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1596007365602315</v>
+        <v>-0.1528877977295802</v>
       </c>
       <c r="J3" t="n">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="K3" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004865379969694605</v>
+        <v>0.004474783196906973</v>
       </c>
       <c r="M3" t="n">
-        <v>12.62314965863472</v>
+        <v>12.63598493001782</v>
       </c>
       <c r="N3" t="n">
-        <v>261.6995255729336</v>
+        <v>261.815760538758</v>
       </c>
       <c r="O3" t="n">
-        <v>16.17712970748932</v>
+        <v>16.18072187940816</v>
       </c>
       <c r="P3" t="n">
-        <v>457.9523140199366</v>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>457.877978495064</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
         <is>
           <t>LINESTRING (174.69283012024246 -36.56150155037064, 174.7026473595283 -36.56400142454656)</t>
@@ -36693,34 +36746,30 @@
         <v>0.0257</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.03952255991197137</v>
+        <v>-0.04155896060146207</v>
       </c>
       <c r="J4" t="n">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="K4" t="n">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0008951958886490585</v>
+        <v>0.0009931094938896434</v>
       </c>
       <c r="M4" t="n">
-        <v>7.006227560467445</v>
+        <v>7.003659083208553</v>
       </c>
       <c r="N4" t="n">
-        <v>87.8665204620112</v>
+        <v>87.76771170866158</v>
       </c>
       <c r="O4" t="n">
-        <v>9.373714336484294</v>
+        <v>9.368442330967383</v>
       </c>
       <c r="P4" t="n">
-        <v>397.8808165965615</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>397.9033611390731</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
         <is>
           <t>LINESTRING (174.6925369563959 -36.56217955684994, 174.70235060198712 -36.56468870554778)</t>
@@ -36775,34 +36824,30 @@
         <v>0.0308</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01070818513145323</v>
+        <v>-0.01434297968183758</v>
       </c>
       <c r="J5" t="n">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="K5" t="n">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="L5" t="n">
-        <v>0.000132929587161712</v>
+        <v>0.0002385004563977278</v>
       </c>
       <c r="M5" t="n">
-        <v>4.707460289072598</v>
+        <v>4.718074104885651</v>
       </c>
       <c r="N5" t="n">
-        <v>43.92143651710362</v>
+        <v>44.01510475619221</v>
       </c>
       <c r="O5" t="n">
-        <v>6.627324989549224</v>
+        <v>6.634388046850456</v>
       </c>
       <c r="P5" t="n">
-        <v>379.8002357151233</v>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>379.8401538835846</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>LINESTRING (174.69235296574726 -36.56267578469191, 174.7019516162302 -36.56567647941682)</t>
@@ -36857,34 +36902,30 @@
         <v>0.0327</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1108012044116833</v>
+        <v>-0.1122652466356234</v>
       </c>
       <c r="J6" t="n">
+        <v>588</v>
+      </c>
+      <c r="K6" t="n">
         <v>587</v>
       </c>
-      <c r="K6" t="n">
-        <v>586</v>
-      </c>
       <c r="L6" t="n">
-        <v>0.0267256155576997</v>
+        <v>0.02749211573079302</v>
       </c>
       <c r="M6" t="n">
-        <v>3.603818791689439</v>
+        <v>3.604348647486254</v>
       </c>
       <c r="N6" t="n">
-        <v>22.54948789250881</v>
+        <v>22.53804808806319</v>
       </c>
       <c r="O6" t="n">
-        <v>4.748630106937032</v>
+        <v>4.747425416798371</v>
       </c>
       <c r="P6" t="n">
-        <v>379.1683989904149</v>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>379.1845590564373</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>LINESTRING (174.6921056563477 -36.563047881779276, 174.70132116587612 -36.566746707781476)</t>
@@ -36939,34 +36980,30 @@
         <v>0.0372</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03939750130782981</v>
+        <v>-0.03955088271882354</v>
       </c>
       <c r="J7" t="n">
+        <v>588</v>
+      </c>
+      <c r="K7" t="n">
         <v>587</v>
       </c>
-      <c r="K7" t="n">
-        <v>586</v>
-      </c>
       <c r="L7" t="n">
-        <v>0.004165508035954946</v>
+        <v>0.004214593533266475</v>
       </c>
       <c r="M7" t="n">
-        <v>3.375267083033719</v>
+        <v>3.370360004993065</v>
       </c>
       <c r="N7" t="n">
-        <v>18.71529553818372</v>
+        <v>18.68370865513142</v>
       </c>
       <c r="O7" t="n">
-        <v>4.326117836835206</v>
+        <v>4.322465575933649</v>
       </c>
       <c r="P7" t="n">
-        <v>381.1437971298184</v>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>381.1454901504757</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>LINESTRING (174.6915552344035 -36.563915721329565, 174.70110041145315 -36.567025301534734)</t>
@@ -37021,34 +37058,30 @@
         <v>0.0354</v>
       </c>
       <c r="I8" t="n">
-        <v>0.005438999720699897</v>
+        <v>0.006179013995840606</v>
       </c>
       <c r="J8" t="n">
+        <v>588</v>
+      </c>
+      <c r="K8" t="n">
         <v>587</v>
       </c>
-      <c r="K8" t="n">
-        <v>586</v>
-      </c>
       <c r="L8" t="n">
-        <v>0.0001397351130922875</v>
+        <v>0.00018094567145166</v>
       </c>
       <c r="M8" t="n">
-        <v>2.44629088494472</v>
+        <v>2.445843842585389</v>
       </c>
       <c r="N8" t="n">
-        <v>10.67608385512945</v>
+        <v>10.66478814595832</v>
       </c>
       <c r="O8" t="n">
-        <v>3.267427712303587</v>
+        <v>3.26569872247247</v>
       </c>
       <c r="P8" t="n">
-        <v>377.9233981495021</v>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>377.9152298881308</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>LINESTRING (174.6911456345122 -36.56493259543049, 174.7010506964073 -36.56719734754784)</t>
@@ -37103,34 +37136,30 @@
         <v>0.0516</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07945774163440569</v>
+        <v>0.08002916116844289</v>
       </c>
       <c r="J9" t="n">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="K9" t="n">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03256229426371859</v>
+        <v>0.03313100220826248</v>
       </c>
       <c r="M9" t="n">
-        <v>2.307202673743596</v>
+        <v>2.306031494831376</v>
       </c>
       <c r="N9" t="n">
-        <v>9.473916936989186</v>
+        <v>9.461867483770593</v>
       </c>
       <c r="O9" t="n">
-        <v>3.077972861639489</v>
+        <v>3.076014870537949</v>
       </c>
       <c r="P9" t="n">
-        <v>377.5944840889538</v>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>377.5881787940522</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
         <is>
           <t>LINESTRING (174.69085855044025 -36.565766975561, 174.70087878983145 -36.567675129607984)</t>
@@ -37185,34 +37214,30 @@
         <v>0.0608</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.0002708172673536895</v>
+        <v>0.001340599197123369</v>
       </c>
       <c r="J10" t="n">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="K10" t="n">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L10" t="n">
-        <v>4.121918127930613e-07</v>
+        <v>1.010401013978868e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>2.229316765553964</v>
+        <v>2.233574431275156</v>
       </c>
       <c r="N10" t="n">
-        <v>9.012336853560379</v>
+        <v>9.029784945741357</v>
       </c>
       <c r="O10" t="n">
-        <v>3.002055438122417</v>
+        <v>3.004960057262219</v>
       </c>
       <c r="P10" t="n">
-        <v>387.1735534406368</v>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>387.1557843621369</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
         <is>
           <t>LINESTRING (174.69058759461748 -36.566829489138364, 174.70081122060876 -36.56781483052222)</t>
@@ -37267,34 +37292,30 @@
         <v>0.0586</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0006133756688680062</v>
+        <v>-0.001762296639535067</v>
       </c>
       <c r="J11" t="n">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="K11" t="n">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L11" t="n">
-        <v>1.743316888958013e-06</v>
+        <v>1.442609375978954e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>2.458668087850325</v>
+        <v>2.458658961376154</v>
       </c>
       <c r="N11" t="n">
-        <v>10.93100889367629</v>
+        <v>10.92900612288365</v>
       </c>
       <c r="O11" t="n">
-        <v>3.306207630152148</v>
+        <v>3.305904735905687</v>
       </c>
       <c r="P11" t="n">
-        <v>388.4525591848005</v>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>388.4652283286053</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>LINESTRING (174.6905189034452 -36.5678211818805, 174.7008091145461 -36.568113925691605)</t>
@@ -37349,34 +37370,30 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01847796496669135</v>
+        <v>0.01749981552300049</v>
       </c>
       <c r="J12" t="n">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="K12" t="n">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001451615685494456</v>
+        <v>0.001306076117124078</v>
       </c>
       <c r="M12" t="n">
-        <v>2.565794132888296</v>
+        <v>2.565554240264345</v>
       </c>
       <c r="N12" t="n">
-        <v>11.896247551181</v>
+        <v>11.88799241893485</v>
       </c>
       <c r="O12" t="n">
-        <v>3.44909372896432</v>
+        <v>3.447896810946472</v>
       </c>
       <c r="P12" t="n">
-        <v>393.8466213981096</v>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>393.8574074454368</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
         <is>
           <t>LINESTRING (174.6904741649465 -36.56868344046451, 174.70077050139966 -36.568614409596115)</t>
@@ -37431,34 +37448,30 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.07557188238839149</v>
+        <v>0.07401695558868195</v>
       </c>
       <c r="J13" t="n">
+        <v>588</v>
+      </c>
+      <c r="K13" t="n">
         <v>587</v>
       </c>
-      <c r="K13" t="n">
-        <v>586</v>
-      </c>
       <c r="L13" t="n">
-        <v>0.02384768651548319</v>
+        <v>0.0229306186359709</v>
       </c>
       <c r="M13" t="n">
-        <v>2.476615545159184</v>
+        <v>2.479181724556522</v>
       </c>
       <c r="N13" t="n">
-        <v>11.79049282203377</v>
+        <v>11.8008348509197</v>
       </c>
       <c r="O13" t="n">
-        <v>3.433728705362986</v>
+        <v>3.435234322563703</v>
       </c>
       <c r="P13" t="n">
-        <v>389.3872152243285</v>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>389.404378472309</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
         <is>
           <t>LINESTRING (174.69054788688584 -36.569822788481495, 174.70074638914477 -36.568679822132616)</t>
@@ -37513,34 +37526,30 @@
         <v>0.1502</v>
       </c>
       <c r="I14" t="n">
-        <v>0.04762475163841496</v>
+        <v>0.04587239758340072</v>
       </c>
       <c r="J14" t="n">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="K14" t="n">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="L14" t="n">
-        <v>0.009700995824704961</v>
+        <v>0.009012742380357652</v>
       </c>
       <c r="M14" t="n">
-        <v>2.700286521161926</v>
+        <v>2.7029698436664</v>
       </c>
       <c r="N14" t="n">
-        <v>11.66728379189156</v>
+        <v>11.68597757645049</v>
       </c>
       <c r="O14" t="n">
-        <v>3.415740592008058</v>
+        <v>3.418475914270933</v>
       </c>
       <c r="P14" t="n">
-        <v>385.6192533284306</v>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Hidden</t>
-        </is>
-      </c>
+        <v>385.6386304348523</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>LINESTRING (174.6907988384256 -36.570795772698744, 174.7008348462634 -36.568941036356215)</t>
@@ -37576,7 +37585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O588"/>
+  <dimension ref="A1:O589"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82659,6 +82668,83 @@
         </is>
       </c>
     </row>
+    <row r="589">
+      <c r="A589" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-10 22:05:38+00:00</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>-36.56198453008241,174.69770525176168</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>-36.56278194241243,174.69785785852935</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>-36.563245199682974,174.69670437197885</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>-36.56387937917535,174.69620264398307</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>-36.56454238957791,174.69582885131263</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>-36.56519720024243,174.69548848412404</t>
+        </is>
+      </c>
+      <c r="H589" t="inlineStr">
+        <is>
+          <t>-36.56586683894671,174.69523110685682</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr">
+        <is>
+          <t>-36.56655655494074,174.69500424682508</t>
+        </is>
+      </c>
+      <c r="J589" t="inlineStr">
+        <is>
+          <t>-36.567248259773166,174.694931493035</t>
+        </is>
+      </c>
+      <c r="K589" t="inlineStr">
+        <is>
+          <t>-36.567943683692,174.69482113977438</t>
+        </is>
+      </c>
+      <c r="L589" t="inlineStr">
+        <is>
+          <t>-36.568654210786924,174.6948501465303</t>
+        </is>
+      </c>
+      <c r="M589" t="inlineStr">
+        <is>
+          <t>-36.569342708911186,174.69483253985996</t>
+        </is>
+      </c>
+      <c r="N589" t="inlineStr">
+        <is>
+          <t>-36.57002676524819,174.69496055940812</t>
+        </is>
+      </c>
+      <c r="O589" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0137/nzd0137.xlsx
+++ b/data/nzd0137/nzd0137.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O589"/>
+  <dimension ref="A1:O591"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30393,6 +30393,108 @@
         <v>382.12</v>
       </c>
       <c r="O589" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="n">
+        <v>426.58</v>
+      </c>
+      <c r="C590" t="n">
+        <v>473</v>
+      </c>
+      <c r="D590" t="n">
+        <v>390.05</v>
+      </c>
+      <c r="E590" t="n">
+        <v>369.32</v>
+      </c>
+      <c r="F590" t="n">
+        <v>371.54</v>
+      </c>
+      <c r="G590" t="n">
+        <v>380.78</v>
+      </c>
+      <c r="H590" t="n">
+        <v>382.89</v>
+      </c>
+      <c r="I590" t="n">
+        <v>380.03</v>
+      </c>
+      <c r="J590" t="n">
+        <v>390.5</v>
+      </c>
+      <c r="K590" t="n">
+        <v>384.44</v>
+      </c>
+      <c r="L590" t="n">
+        <v>390.96</v>
+      </c>
+      <c r="M590" t="n">
+        <v>387.21</v>
+      </c>
+      <c r="N590" t="n">
+        <v>381.55</v>
+      </c>
+      <c r="O590" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="n">
+        <v>422.74</v>
+      </c>
+      <c r="C591" t="n">
+        <v>487.08</v>
+      </c>
+      <c r="D591" t="n">
+        <v>391.49</v>
+      </c>
+      <c r="E591" t="n">
+        <v>370.01</v>
+      </c>
+      <c r="F591" t="n">
+        <v>371.93</v>
+      </c>
+      <c r="G591" t="n">
+        <v>382.15</v>
+      </c>
+      <c r="H591" t="n">
+        <v>383.01</v>
+      </c>
+      <c r="I591" t="n">
+        <v>380.6</v>
+      </c>
+      <c r="J591" t="n">
+        <v>391.21</v>
+      </c>
+      <c r="K591" t="n">
+        <v>385.19</v>
+      </c>
+      <c r="L591" t="n">
+        <v>392.07</v>
+      </c>
+      <c r="M591" t="n">
+        <v>389.08</v>
+      </c>
+      <c r="N591" t="n">
+        <v>383.56</v>
+      </c>
+      <c r="O591" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -30409,7 +30511,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B601"/>
+  <dimension ref="A1:B603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36422,6 +36524,26 @@
       </c>
       <c r="B601" t="n">
         <v>-0.21</v>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="n">
+        <v>0.41</v>
+      </c>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B603" t="n">
+        <v>-0.67</v>
       </c>
     </row>
   </sheetData>
@@ -36590,28 +36712,28 @@
         <v>0.0117</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.04740220468846788</v>
+        <v>-0.07449106440109682</v>
       </c>
       <c r="J2" t="n">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="K2" t="n">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0001935245630778626</v>
+        <v>0.0004777420126448328</v>
       </c>
       <c r="M2" t="n">
-        <v>18.84094234317247</v>
+        <v>18.87954082769039</v>
       </c>
       <c r="N2" t="n">
-        <v>588.3073682568007</v>
+        <v>590.9604555721513</v>
       </c>
       <c r="O2" t="n">
-        <v>24.2550483045654</v>
+        <v>24.30967822847829</v>
       </c>
       <c r="P2" t="n">
-        <v>462.8011584833621</v>
+        <v>463.1028255910848</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36668,28 +36790,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1528877977295802</v>
+        <v>-0.1337060144239598</v>
       </c>
       <c r="J3" t="n">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="K3" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="L3" t="n">
-        <v>0.004474783196906973</v>
+        <v>0.00342089399603851</v>
       </c>
       <c r="M3" t="n">
-        <v>12.63598493001782</v>
+        <v>12.69120028791729</v>
       </c>
       <c r="N3" t="n">
-        <v>261.815760538758</v>
+        <v>263.4102801138441</v>
       </c>
       <c r="O3" t="n">
-        <v>16.18072187940816</v>
+        <v>16.22991928858071</v>
       </c>
       <c r="P3" t="n">
-        <v>457.877978495064</v>
+        <v>457.665285189518</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36746,28 +36868,28 @@
         <v>0.0257</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04155896060146207</v>
+        <v>-0.04596400310391437</v>
       </c>
       <c r="J4" t="n">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="K4" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0009931094938896434</v>
+        <v>0.001222494784890338</v>
       </c>
       <c r="M4" t="n">
-        <v>7.003659083208553</v>
+        <v>7.000032303462768</v>
       </c>
       <c r="N4" t="n">
-        <v>87.76771170866158</v>
+        <v>87.5919702590221</v>
       </c>
       <c r="O4" t="n">
-        <v>9.368442330967383</v>
+        <v>9.35905819294987</v>
       </c>
       <c r="P4" t="n">
-        <v>397.9033611390731</v>
+        <v>397.9521850863216</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36824,28 +36946,28 @@
         <v>0.0308</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.01434297968183758</v>
+        <v>-0.02142404089739353</v>
       </c>
       <c r="J5" t="n">
+        <v>590</v>
+      </c>
+      <c r="K5" t="n">
         <v>588</v>
       </c>
-      <c r="K5" t="n">
-        <v>586</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.0002385004563977278</v>
+        <v>0.0005322901929103452</v>
       </c>
       <c r="M5" t="n">
-        <v>4.718074104885651</v>
+        <v>4.738831890826805</v>
       </c>
       <c r="N5" t="n">
-        <v>44.01510475619221</v>
+        <v>44.18831710972074</v>
       </c>
       <c r="O5" t="n">
-        <v>6.634388046850456</v>
+        <v>6.647429361017741</v>
       </c>
       <c r="P5" t="n">
-        <v>379.8401538835846</v>
+        <v>379.918013856208</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -36902,28 +37024,28 @@
         <v>0.0327</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1122652466356234</v>
+        <v>-0.1155127148736807</v>
       </c>
       <c r="J6" t="n">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="K6" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02749211573079302</v>
+        <v>0.02920002969132252</v>
       </c>
       <c r="M6" t="n">
-        <v>3.604348647486254</v>
+        <v>3.606810112268915</v>
       </c>
       <c r="N6" t="n">
-        <v>22.53804808806319</v>
+        <v>22.52853950816657</v>
       </c>
       <c r="O6" t="n">
-        <v>4.747425416798371</v>
+        <v>4.746423865202788</v>
       </c>
       <c r="P6" t="n">
-        <v>379.1845590564373</v>
+        <v>379.2204472846029</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -36980,28 +37102,28 @@
         <v>0.0372</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03955088271882354</v>
+        <v>-0.03855136991002178</v>
       </c>
       <c r="J7" t="n">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="K7" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004214593533266475</v>
+        <v>0.004035335030690534</v>
       </c>
       <c r="M7" t="n">
-        <v>3.370360004993065</v>
+        <v>3.362682991810503</v>
       </c>
       <c r="N7" t="n">
-        <v>18.68370865513142</v>
+        <v>18.62820282581961</v>
       </c>
       <c r="O7" t="n">
-        <v>4.322465575933649</v>
+        <v>4.316040178893103</v>
       </c>
       <c r="P7" t="n">
-        <v>381.1454901504757</v>
+        <v>381.1344415204853</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37058,28 +37180,28 @@
         <v>0.0354</v>
       </c>
       <c r="I8" t="n">
-        <v>0.006179013995840606</v>
+        <v>0.00972211736473937</v>
       </c>
       <c r="J8" t="n">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="K8" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00018094567145166</v>
+        <v>0.0004480611996953154</v>
       </c>
       <c r="M8" t="n">
-        <v>2.445843842585389</v>
+        <v>2.455472321284347</v>
       </c>
       <c r="N8" t="n">
-        <v>10.66478814595832</v>
+        <v>10.70820660735227</v>
       </c>
       <c r="O8" t="n">
-        <v>3.26569872247247</v>
+        <v>3.272339622861947</v>
       </c>
       <c r="P8" t="n">
-        <v>377.9152298881308</v>
+        <v>377.8760735093038</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37136,28 +37258,28 @@
         <v>0.0516</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08002916116844289</v>
+        <v>0.08046445191870795</v>
       </c>
       <c r="J9" t="n">
+        <v>590</v>
+      </c>
+      <c r="K9" t="n">
         <v>588</v>
       </c>
-      <c r="K9" t="n">
-        <v>586</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.03313100220826248</v>
+        <v>0.03373402706322148</v>
       </c>
       <c r="M9" t="n">
-        <v>2.306031494831376</v>
+        <v>2.300296662338185</v>
       </c>
       <c r="N9" t="n">
-        <v>9.461867483770593</v>
+        <v>9.431167991203036</v>
       </c>
       <c r="O9" t="n">
-        <v>3.076014870537949</v>
+        <v>3.071020675801945</v>
       </c>
       <c r="P9" t="n">
-        <v>377.5881787940522</v>
+        <v>377.5833686543467</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37214,28 +37336,28 @@
         <v>0.0608</v>
       </c>
       <c r="I10" t="n">
-        <v>0.001340599197123369</v>
+        <v>0.004003936650067688</v>
       </c>
       <c r="J10" t="n">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="K10" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L10" t="n">
-        <v>1.010401013978868e-05</v>
+        <v>9.038437135111543e-05</v>
       </c>
       <c r="M10" t="n">
-        <v>2.233574431275156</v>
+        <v>2.239467047187839</v>
       </c>
       <c r="N10" t="n">
-        <v>9.029784945741357</v>
+        <v>9.044646754273638</v>
       </c>
       <c r="O10" t="n">
-        <v>3.004960057262219</v>
+        <v>3.007431920139446</v>
       </c>
       <c r="P10" t="n">
-        <v>387.1557843621369</v>
+        <v>387.1263784771627</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37292,28 +37414,28 @@
         <v>0.0586</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.001762296639535067</v>
+        <v>-0.004381153919171946</v>
       </c>
       <c r="J11" t="n">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="K11" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L11" t="n">
-        <v>1.442609375978954e-05</v>
+        <v>8.950157862008812e-05</v>
       </c>
       <c r="M11" t="n">
-        <v>2.458658961376154</v>
+        <v>2.459786164717947</v>
       </c>
       <c r="N11" t="n">
-        <v>10.92900612288365</v>
+        <v>10.93596890788408</v>
       </c>
       <c r="O11" t="n">
-        <v>3.305904735905687</v>
+        <v>3.306957651359339</v>
       </c>
       <c r="P11" t="n">
-        <v>388.4652283286053</v>
+        <v>388.4941403052542</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37370,28 +37492,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01749981552300049</v>
+        <v>0.01545712512225759</v>
       </c>
       <c r="J12" t="n">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="K12" t="n">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001306076117124078</v>
+        <v>0.001025001304065354</v>
       </c>
       <c r="M12" t="n">
-        <v>2.565554240264345</v>
+        <v>2.565456979668022</v>
       </c>
       <c r="N12" t="n">
-        <v>11.88799241893485</v>
+        <v>11.87510499204871</v>
       </c>
       <c r="O12" t="n">
-        <v>3.447896810946472</v>
+        <v>3.446027421836442</v>
       </c>
       <c r="P12" t="n">
-        <v>393.8574074454368</v>
+        <v>393.8799575815478</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37448,28 +37570,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.07401695558868195</v>
+        <v>0.07166827142951383</v>
       </c>
       <c r="J13" t="n">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="K13" t="n">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0229306186359709</v>
+        <v>0.02162964497040876</v>
       </c>
       <c r="M13" t="n">
-        <v>2.479181724556522</v>
+        <v>2.481052518744587</v>
       </c>
       <c r="N13" t="n">
-        <v>11.8008348509197</v>
+        <v>11.7987160116757</v>
       </c>
       <c r="O13" t="n">
-        <v>3.435234322563703</v>
+        <v>3.434925910653051</v>
       </c>
       <c r="P13" t="n">
-        <v>389.404378472309</v>
+        <v>389.4303310690526</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37526,28 +37648,28 @@
         <v>0.1502</v>
       </c>
       <c r="I14" t="n">
-        <v>0.04587239758340072</v>
+        <v>0.04273557083143871</v>
       </c>
       <c r="J14" t="n">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="K14" t="n">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="L14" t="n">
-        <v>0.009012742380357652</v>
+        <v>0.007849707556249585</v>
       </c>
       <c r="M14" t="n">
-        <v>2.7029698436664</v>
+        <v>2.706866288963262</v>
       </c>
       <c r="N14" t="n">
-        <v>11.68597757645049</v>
+        <v>11.71205034672339</v>
       </c>
       <c r="O14" t="n">
-        <v>3.418475914270933</v>
+        <v>3.422287297513666</v>
       </c>
       <c r="P14" t="n">
-        <v>385.6386304348523</v>
+        <v>385.6733549850595</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37585,7 +37707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O589"/>
+  <dimension ref="A1:O591"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82745,6 +82867,160 @@
         </is>
       </c>
     </row>
+    <row r="590">
+      <c r="A590" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-17 22:11:50+00:00</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>-36.56196916153166,174.69764121691293</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>-36.562784872371154,174.69786936480813</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>-36.56324176860158,174.6966909529191</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>-36.56387863012365,174.69620024799</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>-36.564539619331256,174.69582194952412</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>-36.5652009127192,174.69549987962554</t>
+        </is>
+      </c>
+      <c r="H590" t="inlineStr">
+        <is>
+          <t>-36.56587374544589,174.69526131183832</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>-36.56655400787886,174.69499087208087</t>
+        </is>
+      </c>
+      <c r="J590" t="inlineStr">
+        <is>
+          <t>-36.56724712632616,174.69491973352476</t>
+        </is>
+      </c>
+      <c r="K590" t="inlineStr">
+        <is>
+          <t>-36.56794341043801,174.6948115370585</t>
+        </is>
+      </c>
+      <c r="L590" t="inlineStr">
+        <is>
+          <t>-36.56865426391836,174.69484221397616</t>
+        </is>
+      </c>
+      <c r="M590" t="inlineStr">
+        <is>
+          <t>-36.56934264690118,174.69483309320012</t>
+        </is>
+      </c>
+      <c r="N590" t="inlineStr">
+        <is>
+          <t>-36.57002791246643,174.694954351526</t>
+        </is>
+      </c>
+      <c r="O590" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>-36.56195929274476,174.69760009755788</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>-36.5628230702475,174.69801937266672</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>-36.56324568983733,174.69670628898749</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr">
+        <is>
+          <t>-36.56388087727859,174.69620743596937</t>
+        </is>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>-36.56454118512289,174.69582585053496</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>-36.56520553643872,174.69551407220618</t>
+        </is>
+      </c>
+      <c r="H591" t="inlineStr">
+        <is>
+          <t>-36.565874040385175,174.69526260173086</t>
+        </is>
+      </c>
+      <c r="I591" t="inlineStr">
+        <is>
+          <t>-36.5665551882248,174.69499707013296</t>
+        </is>
+      </c>
+      <c r="J591" t="inlineStr">
+        <is>
+          <t>-36.56724788552192,174.6949276101778</t>
+        </is>
+      </c>
+      <c r="K591" t="inlineStr">
+        <is>
+          <t>-36.56794364874094,174.69481991152003</t>
+        </is>
+      </c>
+      <c r="L591" t="inlineStr">
+        <is>
+          <t>-36.568654180853486,174.69485461557488</t>
+        </is>
+      </c>
+      <c r="M591" t="inlineStr">
+        <is>
+          <t>-36.56934032772478,174.69485378812092</t>
+        </is>
+      </c>
+      <c r="N591" t="inlineStr">
+        <is>
+          <t>-36.57002386701124,174.69497624247776</t>
+        </is>
+      </c>
+      <c r="O591" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0137/nzd0137.xlsx
+++ b/data/nzd0137/nzd0137.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O591"/>
+  <dimension ref="A1:O594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30497,6 +30497,159 @@
       <c r="O591" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B592" t="n">
+        <v>422.74</v>
+      </c>
+      <c r="C592" t="n">
+        <v>489.44</v>
+      </c>
+      <c r="D592" t="n">
+        <v>391.49</v>
+      </c>
+      <c r="E592" t="n">
+        <v>369.76</v>
+      </c>
+      <c r="F592" t="n">
+        <v>371.34</v>
+      </c>
+      <c r="G592" t="n">
+        <v>381.84</v>
+      </c>
+      <c r="H592" t="n">
+        <v>382.69</v>
+      </c>
+      <c r="I592" t="n">
+        <v>378.43</v>
+      </c>
+      <c r="J592" t="n">
+        <v>390.55</v>
+      </c>
+      <c r="K592" t="n">
+        <v>384.95</v>
+      </c>
+      <c r="L592" t="n">
+        <v>392.36</v>
+      </c>
+      <c r="M592" t="n">
+        <v>390.86</v>
+      </c>
+      <c r="N592" t="n">
+        <v>383.63</v>
+      </c>
+      <c r="O592" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B593" t="n">
+        <v>417.8</v>
+      </c>
+      <c r="C593" t="n">
+        <v>488.31</v>
+      </c>
+      <c r="D593" t="n">
+        <v>390.74</v>
+      </c>
+      <c r="E593" t="n">
+        <v>371.36</v>
+      </c>
+      <c r="F593" t="n">
+        <v>372.18</v>
+      </c>
+      <c r="G593" t="n">
+        <v>382.64</v>
+      </c>
+      <c r="H593" t="n">
+        <v>384.57</v>
+      </c>
+      <c r="I593" t="n">
+        <v>379.45</v>
+      </c>
+      <c r="J593" t="n">
+        <v>391.01</v>
+      </c>
+      <c r="K593" t="n">
+        <v>385.83</v>
+      </c>
+      <c r="L593" t="n">
+        <v>392.64</v>
+      </c>
+      <c r="M593" t="n">
+        <v>390.98</v>
+      </c>
+      <c r="N593" t="n">
+        <v>384.42</v>
+      </c>
+      <c r="O593" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B594" t="n">
+        <v>417.8</v>
+      </c>
+      <c r="C594" t="n">
+        <v>488.31</v>
+      </c>
+      <c r="D594" t="n">
+        <v>390.74</v>
+      </c>
+      <c r="E594" t="n">
+        <v>371.36</v>
+      </c>
+      <c r="F594" t="n">
+        <v>372.18</v>
+      </c>
+      <c r="G594" t="n">
+        <v>382.64</v>
+      </c>
+      <c r="H594" t="n">
+        <v>384.57</v>
+      </c>
+      <c r="I594" t="n">
+        <v>379.45</v>
+      </c>
+      <c r="J594" t="n">
+        <v>389.16</v>
+      </c>
+      <c r="K594" t="n">
+        <v>385.97</v>
+      </c>
+      <c r="L594" t="n">
+        <v>391.38</v>
+      </c>
+      <c r="M594" t="n">
+        <v>390.02</v>
+      </c>
+      <c r="N594" t="n">
+        <v>384.64</v>
+      </c>
+      <c r="O594" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -30511,7 +30664,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B603"/>
+  <dimension ref="A1:B606"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36544,6 +36697,36 @@
       </c>
       <c r="B603" t="n">
         <v>-0.67</v>
+      </c>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B604" t="n">
+        <v>-0.59</v>
+      </c>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B605" t="n">
+        <v>1.18</v>
+      </c>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B606" t="n">
+        <v>-0.82</v>
       </c>
     </row>
   </sheetData>
@@ -36712,28 +36895,28 @@
         <v>0.0117</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.07449106440109682</v>
+        <v>-0.1200100108632984</v>
       </c>
       <c r="J2" t="n">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="K2" t="n">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0004777420126448328</v>
+        <v>0.001235110398189465</v>
       </c>
       <c r="M2" t="n">
-        <v>18.87954082769039</v>
+        <v>18.95502978732478</v>
       </c>
       <c r="N2" t="n">
-        <v>590.9604555721513</v>
+        <v>596.8016012188714</v>
       </c>
       <c r="O2" t="n">
-        <v>24.30967822847829</v>
+        <v>24.42952314759482</v>
       </c>
       <c r="P2" t="n">
-        <v>463.1028255910848</v>
+        <v>463.6115670272156</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36790,28 +36973,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1337060144239598</v>
+        <v>-0.09610660827101852</v>
       </c>
       <c r="J3" t="n">
+        <v>593</v>
+      </c>
+      <c r="K3" t="n">
         <v>590</v>
       </c>
-      <c r="K3" t="n">
-        <v>587</v>
-      </c>
       <c r="L3" t="n">
-        <v>0.00342089399603851</v>
+        <v>0.00175172532505774</v>
       </c>
       <c r="M3" t="n">
-        <v>12.69120028791729</v>
+        <v>12.82059268381367</v>
       </c>
       <c r="N3" t="n">
-        <v>263.4102801138441</v>
+        <v>268.0531543145082</v>
       </c>
       <c r="O3" t="n">
-        <v>16.22991928858071</v>
+        <v>16.37232892152207</v>
       </c>
       <c r="P3" t="n">
-        <v>457.665285189518</v>
+        <v>457.2469770904593</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -36868,28 +37051,28 @@
         <v>0.0257</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.04596400310391437</v>
+        <v>-0.05219895472236016</v>
       </c>
       <c r="J4" t="n">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="K4" t="n">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="L4" t="n">
-        <v>0.001222494784890338</v>
+        <v>0.001591961164090994</v>
       </c>
       <c r="M4" t="n">
-        <v>7.000032303462768</v>
+        <v>6.993068281619502</v>
       </c>
       <c r="N4" t="n">
-        <v>87.5919702590221</v>
+        <v>87.31029563912335</v>
       </c>
       <c r="O4" t="n">
-        <v>9.35905819294987</v>
+        <v>9.343997840278183</v>
       </c>
       <c r="P4" t="n">
-        <v>397.9521850863216</v>
+        <v>398.0215421119643</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -36946,28 +37129,28 @@
         <v>0.0308</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.02142404089739353</v>
+        <v>-0.03058618733787379</v>
       </c>
       <c r="J5" t="n">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="K5" t="n">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0005322901929103452</v>
+        <v>0.001088237150927207</v>
       </c>
       <c r="M5" t="n">
-        <v>4.738831890826805</v>
+        <v>4.763378056706409</v>
       </c>
       <c r="N5" t="n">
-        <v>44.18831710972074</v>
+        <v>44.32937424382747</v>
       </c>
       <c r="O5" t="n">
-        <v>6.647429361017741</v>
+        <v>6.658030808266621</v>
       </c>
       <c r="P5" t="n">
-        <v>379.918013856208</v>
+        <v>380.0191056452457</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37024,28 +37207,28 @@
         <v>0.0327</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1155127148736807</v>
+        <v>-0.1200944653929078</v>
       </c>
       <c r="J6" t="n">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="K6" t="n">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02920002969132252</v>
+        <v>0.03173055824364823</v>
       </c>
       <c r="M6" t="n">
-        <v>3.606810112268915</v>
+        <v>3.609231538179754</v>
       </c>
       <c r="N6" t="n">
-        <v>22.52853950816657</v>
+        <v>22.50458260593487</v>
       </c>
       <c r="O6" t="n">
-        <v>4.746423865202788</v>
+        <v>4.743899514738363</v>
       </c>
       <c r="P6" t="n">
-        <v>379.2204472846029</v>
+        <v>379.2712542875572</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37102,28 +37285,28 @@
         <v>0.0372</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03855136991002178</v>
+        <v>-0.03609988418977012</v>
       </c>
       <c r="J7" t="n">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="K7" t="n">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004035335030690534</v>
+        <v>0.00357751681680174</v>
       </c>
       <c r="M7" t="n">
-        <v>3.362682991810503</v>
+        <v>3.354872220363736</v>
       </c>
       <c r="N7" t="n">
-        <v>18.62820282581961</v>
+        <v>18.56008303031771</v>
       </c>
       <c r="O7" t="n">
-        <v>4.316040178893103</v>
+        <v>4.308141482161155</v>
       </c>
       <c r="P7" t="n">
-        <v>381.1344415204853</v>
+        <v>381.1072502598367</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37180,28 +37363,28 @@
         <v>0.0354</v>
       </c>
       <c r="I8" t="n">
-        <v>0.00972211736473937</v>
+        <v>0.01601098204648213</v>
       </c>
       <c r="J8" t="n">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="K8" t="n">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0004480611996953154</v>
+        <v>0.001209324166220993</v>
       </c>
       <c r="M8" t="n">
-        <v>2.455472321284347</v>
+        <v>2.475652995843884</v>
       </c>
       <c r="N8" t="n">
-        <v>10.70820660735227</v>
+        <v>10.82615278553577</v>
       </c>
       <c r="O8" t="n">
-        <v>3.272339622861947</v>
+        <v>3.290311958695675</v>
       </c>
       <c r="P8" t="n">
-        <v>377.8760735093038</v>
+        <v>377.8063199514162</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37258,28 +37441,28 @@
         <v>0.0516</v>
       </c>
       <c r="I9" t="n">
-        <v>0.08046445191870795</v>
+        <v>0.0797950952349054</v>
       </c>
       <c r="J9" t="n">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="K9" t="n">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03373402706322148</v>
+        <v>0.03356814369348105</v>
       </c>
       <c r="M9" t="n">
-        <v>2.300296662338185</v>
+        <v>2.291608142640742</v>
       </c>
       <c r="N9" t="n">
-        <v>9.431167991203036</v>
+        <v>9.386368136893701</v>
       </c>
       <c r="O9" t="n">
-        <v>3.071020675801945</v>
+        <v>3.063718025029996</v>
       </c>
       <c r="P9" t="n">
-        <v>377.5833686543467</v>
+        <v>377.5907841123842</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37336,28 +37519,28 @@
         <v>0.0608</v>
       </c>
       <c r="I10" t="n">
-        <v>0.004003936650067688</v>
+        <v>0.007251140133093756</v>
       </c>
       <c r="J10" t="n">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="K10" t="n">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="L10" t="n">
-        <v>9.038437135111543e-05</v>
+        <v>0.0002983234231244136</v>
       </c>
       <c r="M10" t="n">
-        <v>2.239467047187839</v>
+        <v>2.24442838385051</v>
       </c>
       <c r="N10" t="n">
-        <v>9.044646754273638</v>
+        <v>9.046983261561676</v>
       </c>
       <c r="O10" t="n">
-        <v>3.007431920139446</v>
+        <v>3.007820350612994</v>
       </c>
       <c r="P10" t="n">
-        <v>387.1263784771627</v>
+        <v>387.0904135028271</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37414,28 +37597,28 @@
         <v>0.0586</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.004381153919171946</v>
+        <v>-0.007398525160758607</v>
       </c>
       <c r="J11" t="n">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="K11" t="n">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="L11" t="n">
-        <v>8.950157862008812e-05</v>
+        <v>0.0002573067636921778</v>
       </c>
       <c r="M11" t="n">
-        <v>2.459786164717947</v>
+        <v>2.458438575489526</v>
       </c>
       <c r="N11" t="n">
-        <v>10.93596890788408</v>
+        <v>10.92032264691274</v>
       </c>
       <c r="O11" t="n">
-        <v>3.306957651359339</v>
+        <v>3.304591146709792</v>
       </c>
       <c r="P11" t="n">
-        <v>388.4941403052542</v>
+        <v>388.5275650510519</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37492,28 +37675,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01545712512225759</v>
+        <v>0.01311420865959696</v>
       </c>
       <c r="J12" t="n">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="K12" t="n">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="L12" t="n">
-        <v>0.001025001304065354</v>
+        <v>0.0007453003436733718</v>
       </c>
       <c r="M12" t="n">
-        <v>2.565456979668022</v>
+        <v>2.562220234051116</v>
       </c>
       <c r="N12" t="n">
-        <v>11.87510499204871</v>
+        <v>11.83960410035152</v>
       </c>
       <c r="O12" t="n">
-        <v>3.446027421836442</v>
+        <v>3.440872578337001</v>
       </c>
       <c r="P12" t="n">
-        <v>393.8799575815478</v>
+        <v>393.9059240509471</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37570,28 +37753,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.07166827142951383</v>
+        <v>0.07088472279779987</v>
       </c>
       <c r="J13" t="n">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="K13" t="n">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02162964497040876</v>
+        <v>0.02141177958766305</v>
       </c>
       <c r="M13" t="n">
-        <v>2.481052518744587</v>
+        <v>2.471932926984484</v>
       </c>
       <c r="N13" t="n">
-        <v>11.7987160116757</v>
+        <v>11.74245685805411</v>
       </c>
       <c r="O13" t="n">
-        <v>3.434925910653051</v>
+        <v>3.426726843221402</v>
       </c>
       <c r="P13" t="n">
-        <v>389.4303310690526</v>
+        <v>389.4390274343511</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37648,28 +37831,28 @@
         <v>0.1502</v>
       </c>
       <c r="I14" t="n">
-        <v>0.04273557083143871</v>
+        <v>0.03993524269889156</v>
       </c>
       <c r="J14" t="n">
+        <v>593</v>
+      </c>
+      <c r="K14" t="n">
         <v>590</v>
       </c>
-      <c r="K14" t="n">
-        <v>587</v>
-      </c>
       <c r="L14" t="n">
-        <v>0.007849707556249585</v>
+        <v>0.006923031039444472</v>
       </c>
       <c r="M14" t="n">
-        <v>2.706866288963262</v>
+        <v>2.704740742206353</v>
       </c>
       <c r="N14" t="n">
-        <v>11.71205034672339</v>
+        <v>11.68685510610062</v>
       </c>
       <c r="O14" t="n">
-        <v>3.422287297513666</v>
+        <v>3.418604262868199</v>
       </c>
       <c r="P14" t="n">
-        <v>385.6733549850595</v>
+        <v>385.7044606649764</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37707,7 +37890,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O591"/>
+  <dimension ref="A1:O594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83021,6 +83204,237 @@
         </is>
       </c>
     </row>
+    <row r="592">
+      <c r="A592" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:26+00:00</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>-36.56195929274476,174.69760009755788</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>-36.562829472713574,174.69804451604315</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>-36.56324568983733,174.69670628898749</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr">
+        <is>
+          <t>-36.56388006309207,174.696204831629</t>
+        </is>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>-36.564538816361136,174.69581994900577</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>-36.565204490195775,174.6955108607462</t>
+        </is>
+      </c>
+      <c r="H592" t="inlineStr">
+        <is>
+          <t>-36.56587325388038,174.69525916201738</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>-36.56655069462533,174.69497347404078</t>
+        </is>
+      </c>
+      <c r="J592" t="inlineStr">
+        <is>
+          <t>-36.567247179790655,174.6949202882186</t>
+        </is>
+      </c>
+      <c r="K592" t="inlineStr">
+        <is>
+          <t>-36.56794357248407,174.69481723169233</t>
+        </is>
+      </c>
+      <c r="L592" t="inlineStr">
+        <is>
+          <t>-36.56865415915165,174.6948578556322</t>
+        </is>
+      </c>
+      <c r="M592" t="inlineStr">
+        <is>
+          <t>-36.5693381201632,174.6948734870282</t>
+        </is>
+      </c>
+      <c r="N592" t="inlineStr">
+        <is>
+          <t>-36.57002372612467,174.6949770048492</t>
+        </is>
+      </c>
+      <c r="O592" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-21 22:11:34+00:00</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>-36.56194659694034,174.6975471992356</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>-36.562826407126686,174.6980324770531</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>-36.5632436475273,174.6966983014517</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr">
+        <is>
+          <t>-36.5638852738848,174.6962214994085</t>
+        </is>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>-36.56454218883541,174.69582835118302</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>-36.565207190177404,174.69551914838505</t>
+        </is>
+      </c>
+      <c r="H593" t="inlineStr">
+        <is>
+          <t>-36.5658778745947,174.69527937033502</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>-36.56655280682475,174.69498456529118</t>
+        </is>
+      </c>
+      <c r="J593" t="inlineStr">
+        <is>
+          <t>-36.56724767166401,174.69492539140228</t>
+        </is>
+      </c>
+      <c r="K593" t="inlineStr">
+        <is>
+          <t>-36.567943852092306,174.6948270577272</t>
+        </is>
+      </c>
+      <c r="L593" t="inlineStr">
+        <is>
+          <t>-36.56865413819806,174.6948609839634</t>
+        </is>
+      </c>
+      <c r="M593" t="inlineStr">
+        <is>
+          <t>-36.569337971338705,174.69487481504436</t>
+        </is>
+      </c>
+      <c r="N593" t="inlineStr">
+        <is>
+          <t>-36.57002213611876,174.69498560875488</t>
+        </is>
+      </c>
+      <c r="O593" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-14 22:11:35+00:00</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>-36.56194659694034,174.6975471992356</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>-36.562826407126686,174.6980324770531</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>-36.5632436475273,174.6966983014517</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>-36.5638852738848,174.6962214994085</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>-36.56454218883541,174.69582835118302</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>-36.565207190177404,174.69551914838505</t>
+        </is>
+      </c>
+      <c r="H594" t="inlineStr">
+        <is>
+          <t>-36.5658778745947,174.69527937033502</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>-36.56655280682475,174.69498456529118</t>
+        </is>
+      </c>
+      <c r="J594" t="inlineStr">
+        <is>
+          <t>-36.567245693476366,174.69490486772918</t>
+        </is>
+      </c>
+      <c r="K594" t="inlineStr">
+        <is>
+          <t>-36.56794389657538,174.69482862096004</t>
+        </is>
+      </c>
+      <c r="L594" t="inlineStr">
+        <is>
+          <t>-36.56865423248856,174.694846906473</t>
+        </is>
+      </c>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>-36.56933916193423,174.6948641909148</t>
+        </is>
+      </c>
+      <c r="N594" t="inlineStr">
+        <is>
+          <t>-36.57002169333219,174.69498800477922</t>
+        </is>
+      </c>
+      <c r="O594" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0137/nzd0137.xlsx
+++ b/data/nzd0137/nzd0137.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O594"/>
+  <dimension ref="A1:O600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30648,6 +30648,312 @@
         <v>384.64</v>
       </c>
       <c r="O594" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="n">
+        <v>420.21</v>
+      </c>
+      <c r="C595" t="n">
+        <v>480.8</v>
+      </c>
+      <c r="D595" t="n">
+        <v>390.63</v>
+      </c>
+      <c r="E595" t="n">
+        <v>371.72</v>
+      </c>
+      <c r="F595" t="n">
+        <v>371.77</v>
+      </c>
+      <c r="G595" t="n">
+        <v>381.48</v>
+      </c>
+      <c r="H595" t="n">
+        <v>384.27</v>
+      </c>
+      <c r="I595" t="n">
+        <v>378.93</v>
+      </c>
+      <c r="J595" t="n">
+        <v>388.78</v>
+      </c>
+      <c r="K595" t="n">
+        <v>386.1</v>
+      </c>
+      <c r="L595" t="n">
+        <v>391.72</v>
+      </c>
+      <c r="M595" t="n">
+        <v>390</v>
+      </c>
+      <c r="N595" t="n">
+        <v>384.89</v>
+      </c>
+      <c r="O595" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="n">
+        <v>413.5</v>
+      </c>
+      <c r="C596" t="n">
+        <v>468.43</v>
+      </c>
+      <c r="D596" t="n">
+        <v>389.72</v>
+      </c>
+      <c r="E596" t="n">
+        <v>370.62</v>
+      </c>
+      <c r="F596" t="n">
+        <v>370.58</v>
+      </c>
+      <c r="G596" t="n">
+        <v>379.92</v>
+      </c>
+      <c r="H596" t="n">
+        <v>382.64</v>
+      </c>
+      <c r="I596" t="n">
+        <v>377.41</v>
+      </c>
+      <c r="J596" t="n">
+        <v>387.84</v>
+      </c>
+      <c r="K596" t="n">
+        <v>385.46</v>
+      </c>
+      <c r="L596" t="n">
+        <v>391.66</v>
+      </c>
+      <c r="M596" t="n">
+        <v>389.5</v>
+      </c>
+      <c r="N596" t="n">
+        <v>384.63</v>
+      </c>
+      <c r="O596" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="n">
+        <v>406.34</v>
+      </c>
+      <c r="C597" t="n">
+        <v>458.79</v>
+      </c>
+      <c r="D597" t="n">
+        <v>391.13</v>
+      </c>
+      <c r="E597" t="n">
+        <v>370.65</v>
+      </c>
+      <c r="F597" t="n">
+        <v>370.14</v>
+      </c>
+      <c r="G597" t="n">
+        <v>378.71</v>
+      </c>
+      <c r="H597" t="n">
+        <v>382.83</v>
+      </c>
+      <c r="I597" t="n">
+        <v>376.53</v>
+      </c>
+      <c r="J597" t="n">
+        <v>388.11</v>
+      </c>
+      <c r="K597" t="n">
+        <v>385.24</v>
+      </c>
+      <c r="L597" t="n">
+        <v>391.7</v>
+      </c>
+      <c r="M597" t="n">
+        <v>387.78</v>
+      </c>
+      <c r="N597" t="n">
+        <v>384.27</v>
+      </c>
+      <c r="O597" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="n">
+        <v>403.18</v>
+      </c>
+      <c r="C598" t="n">
+        <v>452.15</v>
+      </c>
+      <c r="D598" t="n">
+        <v>389.74</v>
+      </c>
+      <c r="E598" t="n">
+        <v>369.55</v>
+      </c>
+      <c r="F598" t="n">
+        <v>369.24</v>
+      </c>
+      <c r="G598" t="n">
+        <v>377.34</v>
+      </c>
+      <c r="H598" t="n">
+        <v>381.49</v>
+      </c>
+      <c r="I598" t="n">
+        <v>375.75</v>
+      </c>
+      <c r="J598" t="n">
+        <v>387.79</v>
+      </c>
+      <c r="K598" t="n">
+        <v>384.88</v>
+      </c>
+      <c r="L598" t="n">
+        <v>391.96</v>
+      </c>
+      <c r="M598" t="n">
+        <v>387.92</v>
+      </c>
+      <c r="N598" t="n">
+        <v>384.73</v>
+      </c>
+      <c r="O598" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="n">
+        <v>402.19</v>
+      </c>
+      <c r="C599" t="n">
+        <v>448.26</v>
+      </c>
+      <c r="D599" t="n">
+        <v>388.52</v>
+      </c>
+      <c r="E599" t="n">
+        <v>368.92</v>
+      </c>
+      <c r="F599" t="n">
+        <v>368.41</v>
+      </c>
+      <c r="G599" t="n">
+        <v>376.04</v>
+      </c>
+      <c r="H599" t="n">
+        <v>380.68</v>
+      </c>
+      <c r="I599" t="n">
+        <v>375.15</v>
+      </c>
+      <c r="J599" t="n">
+        <v>387.22</v>
+      </c>
+      <c r="K599" t="n">
+        <v>384.47</v>
+      </c>
+      <c r="L599" t="n">
+        <v>391.96</v>
+      </c>
+      <c r="M599" t="n">
+        <v>387.52</v>
+      </c>
+      <c r="N599" t="n">
+        <v>384.96</v>
+      </c>
+      <c r="O599" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="n">
+        <v>402.19</v>
+      </c>
+      <c r="C600" t="n">
+        <v>448.26</v>
+      </c>
+      <c r="D600" t="n">
+        <v>388.52</v>
+      </c>
+      <c r="E600" t="n">
+        <v>370.81</v>
+      </c>
+      <c r="F600" t="n">
+        <v>368.85</v>
+      </c>
+      <c r="G600" t="n">
+        <v>376.19</v>
+      </c>
+      <c r="H600" t="n">
+        <v>380.63</v>
+      </c>
+      <c r="I600" t="n">
+        <v>375.61</v>
+      </c>
+      <c r="J600" t="n">
+        <v>387.44</v>
+      </c>
+      <c r="K600" t="n">
+        <v>385.2</v>
+      </c>
+      <c r="L600" t="n">
+        <v>392.34</v>
+      </c>
+      <c r="M600" t="n">
+        <v>387.9</v>
+      </c>
+      <c r="N600" t="n">
+        <v>385.53</v>
+      </c>
+      <c r="O600" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -30664,7 +30970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B606"/>
+  <dimension ref="A1:B612"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -36727,6 +37033,66 @@
       </c>
       <c r="B606" t="n">
         <v>-0.82</v>
+      </c>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B607" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B608" t="n">
+        <v>-0.27</v>
+      </c>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B609" t="n">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B610" t="n">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B611" t="n">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B612" t="n">
+        <v>-0.83</v>
       </c>
     </row>
   </sheetData>
@@ -36895,28 +37261,28 @@
         <v>0.0117</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.1200100108632984</v>
+        <v>-0.2320716926471649</v>
       </c>
       <c r="J2" t="n">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="K2" t="n">
-        <v>576</v>
+        <v>582</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001235110398189465</v>
+        <v>0.004500390512752972</v>
       </c>
       <c r="M2" t="n">
-        <v>18.95502978732478</v>
+        <v>19.19938449759849</v>
       </c>
       <c r="N2" t="n">
-        <v>596.8016012188714</v>
+        <v>618.5421182501509</v>
       </c>
       <c r="O2" t="n">
-        <v>24.42952314759482</v>
+        <v>24.87050699624258</v>
       </c>
       <c r="P2" t="n">
-        <v>463.6115670272156</v>
+        <v>464.8700880039025</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -36973,28 +37339,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.09610660827101852</v>
+        <v>-0.08602037024668494</v>
       </c>
       <c r="J3" t="n">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="K3" t="n">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="L3" t="n">
-        <v>0.00175172532505774</v>
+        <v>0.001428630798985475</v>
       </c>
       <c r="M3" t="n">
-        <v>12.82059268381367</v>
+        <v>12.7968359618687</v>
       </c>
       <c r="N3" t="n">
-        <v>268.0531543145082</v>
+        <v>266.9870365208799</v>
       </c>
       <c r="O3" t="n">
-        <v>16.37232892152207</v>
+        <v>16.33973795753408</v>
       </c>
       <c r="P3" t="n">
-        <v>457.2469770904593</v>
+        <v>457.1345656674033</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37051,28 +37417,28 @@
         <v>0.0257</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.05219895472236016</v>
+        <v>-0.06688580333940207</v>
       </c>
       <c r="J4" t="n">
+        <v>599</v>
+      </c>
+      <c r="K4" t="n">
         <v>593</v>
       </c>
-      <c r="K4" t="n">
-        <v>587</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.001591961164090994</v>
+        <v>0.002658762954492633</v>
       </c>
       <c r="M4" t="n">
-        <v>6.993068281619502</v>
+        <v>6.989815648815706</v>
       </c>
       <c r="N4" t="n">
-        <v>87.31029563912335</v>
+        <v>86.90364849761622</v>
       </c>
       <c r="O4" t="n">
-        <v>9.343997840278183</v>
+        <v>9.322212639583814</v>
       </c>
       <c r="P4" t="n">
-        <v>398.0215421119643</v>
+        <v>398.1856866407542</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37129,28 +37495,28 @@
         <v>0.0308</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.03058618733787379</v>
+        <v>-0.04912978333033163</v>
       </c>
       <c r="J5" t="n">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="K5" t="n">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="L5" t="n">
-        <v>0.001088237150927207</v>
+        <v>0.002820505993931022</v>
       </c>
       <c r="M5" t="n">
-        <v>4.763378056706409</v>
+        <v>4.816591264268036</v>
       </c>
       <c r="N5" t="n">
-        <v>44.32937424382747</v>
+        <v>44.64785143937664</v>
       </c>
       <c r="O5" t="n">
-        <v>6.658030808266621</v>
+        <v>6.68190477628772</v>
       </c>
       <c r="P5" t="n">
-        <v>380.0191056452457</v>
+        <v>380.2246985833642</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37207,28 +37573,28 @@
         <v>0.0327</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1200944653929078</v>
+        <v>-0.1332567441184439</v>
       </c>
       <c r="J6" t="n">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="K6" t="n">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03173055824364823</v>
+        <v>0.03901990789624399</v>
       </c>
       <c r="M6" t="n">
-        <v>3.609231538179754</v>
+        <v>3.635446821525132</v>
       </c>
       <c r="N6" t="n">
-        <v>22.50458260593487</v>
+        <v>22.66691964696918</v>
       </c>
       <c r="O6" t="n">
-        <v>4.743899514738363</v>
+        <v>4.760978853867047</v>
       </c>
       <c r="P6" t="n">
-        <v>379.2712542875572</v>
+        <v>379.4179289475015</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37285,28 +37651,28 @@
         <v>0.0372</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.03609988418977012</v>
+        <v>-0.04004624807289712</v>
       </c>
       <c r="J7" t="n">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="K7" t="n">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00357751681680174</v>
+        <v>0.004485838591188784</v>
       </c>
       <c r="M7" t="n">
-        <v>3.354872220363736</v>
+        <v>3.347543948856894</v>
       </c>
       <c r="N7" t="n">
-        <v>18.56008303031771</v>
+        <v>18.44647657368543</v>
       </c>
       <c r="O7" t="n">
-        <v>4.308141482161155</v>
+        <v>4.294936154785706</v>
       </c>
       <c r="P7" t="n">
-        <v>381.1072502598367</v>
+        <v>381.1512711385392</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37363,28 +37729,28 @@
         <v>0.0354</v>
       </c>
       <c r="I8" t="n">
-        <v>0.01601098204648213</v>
+        <v>0.02415745640880598</v>
       </c>
       <c r="J8" t="n">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="K8" t="n">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="L8" t="n">
-        <v>0.001209324166220993</v>
+        <v>0.002772742440088516</v>
       </c>
       <c r="M8" t="n">
-        <v>2.475652995843884</v>
+        <v>2.493613413411707</v>
       </c>
       <c r="N8" t="n">
-        <v>10.82615278553577</v>
+        <v>10.87859925106157</v>
       </c>
       <c r="O8" t="n">
-        <v>3.290311958695675</v>
+        <v>3.298272161459932</v>
       </c>
       <c r="P8" t="n">
-        <v>377.8063199514162</v>
+        <v>377.7155914420678</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37441,28 +37807,28 @@
         <v>0.0516</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0797950952349054</v>
+        <v>0.07309353959113049</v>
       </c>
       <c r="J9" t="n">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="K9" t="n">
-        <v>591</v>
+        <v>597</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03356814369348105</v>
+        <v>0.02863525097259734</v>
       </c>
       <c r="M9" t="n">
-        <v>2.291608142640742</v>
+        <v>2.2983374671394</v>
       </c>
       <c r="N9" t="n">
-        <v>9.386368136893701</v>
+        <v>9.406025074098382</v>
       </c>
       <c r="O9" t="n">
-        <v>3.063718025029996</v>
+        <v>3.066924367195641</v>
       </c>
       <c r="P9" t="n">
-        <v>377.5907841123842</v>
+        <v>377.6654598670762</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37519,28 +37885,28 @@
         <v>0.0608</v>
       </c>
       <c r="I10" t="n">
-        <v>0.007251140133093756</v>
+        <v>0.008468473378803772</v>
       </c>
       <c r="J10" t="n">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="K10" t="n">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0002983234231244136</v>
+        <v>0.0004162874045924303</v>
       </c>
       <c r="M10" t="n">
-        <v>2.24442838385051</v>
+        <v>2.228197734847846</v>
       </c>
       <c r="N10" t="n">
-        <v>9.046983261561676</v>
+        <v>8.96152446938587</v>
       </c>
       <c r="O10" t="n">
-        <v>3.007820350612994</v>
+        <v>2.993580543326982</v>
       </c>
       <c r="P10" t="n">
-        <v>387.0904135028271</v>
+        <v>387.0768750319695</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37597,28 +37963,28 @@
         <v>0.0586</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.007398525160758607</v>
+        <v>-0.01395883777966065</v>
       </c>
       <c r="J11" t="n">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="K11" t="n">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0002573067636921778</v>
+        <v>0.0009288673828755645</v>
       </c>
       <c r="M11" t="n">
-        <v>2.458438575489526</v>
+        <v>2.458482011914233</v>
       </c>
       <c r="N11" t="n">
-        <v>10.92032264691274</v>
+        <v>10.90653907214113</v>
       </c>
       <c r="O11" t="n">
-        <v>3.304591146709792</v>
+        <v>3.302504969283337</v>
       </c>
       <c r="P11" t="n">
-        <v>388.5275650510519</v>
+        <v>388.6005991050136</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -37675,28 +38041,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.01311420865959696</v>
+        <v>0.008104925571688624</v>
       </c>
       <c r="J12" t="n">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="K12" t="n">
-        <v>589</v>
+        <v>595</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0007453003436733718</v>
+        <v>0.0002902265349932209</v>
       </c>
       <c r="M12" t="n">
-        <v>2.562220234051116</v>
+        <v>2.557157319577902</v>
       </c>
       <c r="N12" t="n">
-        <v>11.83960410035152</v>
+        <v>11.77553437746877</v>
       </c>
       <c r="O12" t="n">
-        <v>3.440872578337001</v>
+        <v>3.431549850646027</v>
       </c>
       <c r="P12" t="n">
-        <v>393.9059240509471</v>
+        <v>393.9616770682803</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -37753,28 +38119,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.07088472279779987</v>
+        <v>0.06473928757920754</v>
       </c>
       <c r="J13" t="n">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="K13" t="n">
-        <v>592</v>
+        <v>598</v>
       </c>
       <c r="L13" t="n">
-        <v>0.02141177958766305</v>
+        <v>0.01820469272560932</v>
       </c>
       <c r="M13" t="n">
-        <v>2.471932926984484</v>
+        <v>2.47406977342964</v>
       </c>
       <c r="N13" t="n">
-        <v>11.74245685805411</v>
+        <v>11.71546117962515</v>
       </c>
       <c r="O13" t="n">
-        <v>3.426726843221402</v>
+        <v>3.422785587737735</v>
       </c>
       <c r="P13" t="n">
-        <v>389.4390274343511</v>
+        <v>389.5075190531298</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -37831,28 +38197,28 @@
         <v>0.1502</v>
       </c>
       <c r="I14" t="n">
-        <v>0.03993524269889156</v>
+        <v>0.0358253042362776</v>
       </c>
       <c r="J14" t="n">
-        <v>593</v>
+        <v>599</v>
       </c>
       <c r="K14" t="n">
-        <v>590</v>
+        <v>596</v>
       </c>
       <c r="L14" t="n">
-        <v>0.006923031039444472</v>
+        <v>0.005692799235296642</v>
       </c>
       <c r="M14" t="n">
-        <v>2.704740742206353</v>
+        <v>2.694439279184912</v>
       </c>
       <c r="N14" t="n">
-        <v>11.68685510610062</v>
+        <v>11.60728852792823</v>
       </c>
       <c r="O14" t="n">
-        <v>3.418604262868199</v>
+        <v>3.406947097905724</v>
       </c>
       <c r="P14" t="n">
-        <v>385.7044606649764</v>
+        <v>385.750328656923</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -37890,7 +38256,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O594"/>
+  <dimension ref="A1:O600"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83435,6 +83801,468 @@
         </is>
       </c>
     </row>
+    <row r="595">
+      <c r="A595" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-22 22:11:20+00:00</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>-36.561952790645485,174.69757300590493</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>-36.56280603315034,174.6979524657351</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>-36.56324334798845,174.69669712994647</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>-36.56388644631283,174.69622524965916</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>-36.56454054274685,174.6958242501202</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>-36.56520327520385,174.69550713130886</t>
+        </is>
+      </c>
+      <c r="H595" t="inlineStr">
+        <is>
+          <t>-36.56587713724689,174.69527614560332</t>
+        </is>
+      </c>
+      <c r="I595" t="inlineStr">
+        <is>
+          <t>-36.56655173001733,174.69497891092814</t>
+        </is>
+      </c>
+      <c r="J595" t="inlineStr">
+        <is>
+          <t>-36.56724528714551,174.69490065205588</t>
+        </is>
+      </c>
+      <c r="K595" t="inlineStr">
+        <is>
+          <t>-36.56794393788106,174.69483007253336</t>
+        </is>
+      </c>
+      <c r="L595" t="inlineStr">
+        <is>
+          <t>-36.56865420704526,174.6948507051609</t>
+        </is>
+      </c>
+      <c r="M595" t="inlineStr">
+        <is>
+          <t>-36.569339186738304,174.6948639695788</t>
+        </is>
+      </c>
+      <c r="N595" t="inlineStr">
+        <is>
+          <t>-36.57002119016557,174.69499072753405</t>
+        </is>
+      </c>
+      <c r="O595" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30 22:11:30+00:00</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>-36.56193554591699,174.69750115415064</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>-36.56277247429736,174.69782067620818</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>-36.563240869984774,174.69668743840364</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>-36.563882863893454,174.69621379056022</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>-36.56453576507433,174.6958123470365</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>-36.56519801023745,174.69549097041516</t>
+        </is>
+      </c>
+      <c r="H596" t="inlineStr">
+        <is>
+          <t>-36.56587313098899,174.69525862456217</t>
+        </is>
+      </c>
+      <c r="I596" t="inlineStr">
+        <is>
+          <t>-36.566548582424886,174.69496238279098</t>
+        </is>
+      </c>
+      <c r="J596" t="inlineStr">
+        <is>
+          <t>-36.567244282010584,174.6948902238116</t>
+        </is>
+      </c>
+      <c r="K596" t="inlineStr">
+        <is>
+          <t>-36.56794373452987,174.69482292632617</t>
+        </is>
+      </c>
+      <c r="L596" t="inlineStr">
+        <is>
+          <t>-36.56865421153527,174.69485003480418</t>
+        </is>
+      </c>
+      <c r="M596" t="inlineStr">
+        <is>
+          <t>-36.569339806839764,174.6948584361778</t>
+        </is>
+      </c>
+      <c r="N596" t="inlineStr">
+        <is>
+          <t>-36.57002171345886,174.694987895869</t>
+        </is>
+      </c>
+      <c r="O596" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="597">
+      <c r="A597" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-09 22:05:35+00:00</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>-36.561917144637825,174.69742448375777</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>-36.56274632161994,174.69771797207673</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>-36.56324470952858,174.69670245497028</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr">
+        <is>
+          <t>-36.56388296159582,174.69621410308108</t>
+        </is>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>-36.56453399853964,174.69580794589666</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>-36.565193926511974,174.6954784353645</t>
+        </is>
+      </c>
+      <c r="H597" t="inlineStr">
+        <is>
+          <t>-36.565873597976235,174.695260666892</t>
+        </is>
+      </c>
+      <c r="I597" t="inlineStr">
+        <is>
+          <t>-36.56654676013344,174.69495281387003</t>
+        </is>
+      </c>
+      <c r="J597" t="inlineStr">
+        <is>
+          <t>-36.567244570719645,174.69489321915836</t>
+        </is>
+      </c>
+      <c r="K597" t="inlineStr">
+        <is>
+          <t>-36.5679436646278,174.69482046981747</t>
+        </is>
+      </c>
+      <c r="L597" t="inlineStr">
+        <is>
+          <t>-36.56865420854193,174.69485048170867</t>
+        </is>
+      </c>
+      <c r="M597" t="inlineStr">
+        <is>
+          <t>-36.56934193998681,174.69483940127773</t>
+        </is>
+      </c>
+      <c r="N597" t="inlineStr">
+        <is>
+          <t>-36.57002243801866,174.69498397510193</t>
+        </is>
+      </c>
+      <c r="O597" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-16 22:11:13+00:00</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>-36.561909023386875,174.69739064599764</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>-36.56272830768995,174.69764722985036</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>-36.5632409244464,174.69668765140457</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr">
+        <is>
+          <t>-36.56387937917535,174.69620264398307</t>
+        </is>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>-36.564530385172716,174.6957989435658</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>-36.56518930278808,174.69546424278795</t>
+        </is>
+      </c>
+      <c r="H598" t="inlineStr">
+        <is>
+          <t>-36.565870304486424,174.69524626309243</t>
+        </is>
+      </c>
+      <c r="I598" t="inlineStr">
+        <is>
+          <t>-36.56654514491992,174.69494433232683</t>
+        </is>
+      </c>
+      <c r="J598" t="inlineStr">
+        <is>
+          <t>-36.567244228545924,174.69488966911777</t>
+        </is>
+      </c>
+      <c r="K598" t="inlineStr">
+        <is>
+          <t>-36.567943550242475,174.69481645007593</t>
+        </is>
+      </c>
+      <c r="L598" t="inlineStr">
+        <is>
+          <t>-36.5686541890852,174.69485338658765</t>
+        </is>
+      </c>
+      <c r="M598" t="inlineStr">
+        <is>
+          <t>-36.56934176635868,174.6948409506301</t>
+        </is>
+      </c>
+      <c r="N598" t="inlineStr">
+        <is>
+          <t>-36.57002151219221,174.69498898497093</t>
+        </is>
+      </c>
+      <c r="O598" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>-36.56190647906891,174.6973800449286</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>-36.56271775432849,174.69760578600037</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>-36.56323760228638,174.69667465834806</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr">
+        <is>
+          <t>-36.563877327424926,174.69619608104563</t>
+        </is>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>-36.56452705284481,174.69579064141692</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>-36.56518491531126,174.6954507753811</t>
+        </is>
+      </c>
+      <c r="H599" t="inlineStr">
+        <is>
+          <t>-36.56586831364469,174.69523755631863</t>
+        </is>
+      </c>
+      <c r="I599" t="inlineStr">
+        <is>
+          <t>-36.56654390244757,174.69493780806306</t>
+        </is>
+      </c>
+      <c r="J599" t="inlineStr">
+        <is>
+          <t>-36.567243619048746,174.69488334560808</t>
+        </is>
+      </c>
+      <c r="K599" t="inlineStr">
+        <is>
+          <t>-36.56794341997014,174.69481187203698</t>
+        </is>
+      </c>
+      <c r="L599" t="inlineStr">
+        <is>
+          <t>-36.5686541890852,174.69485338658765</t>
+        </is>
+      </c>
+      <c r="M599" t="inlineStr">
+        <is>
+          <t>-36.56934226243903,174.694836523909</t>
+        </is>
+      </c>
+      <c r="N599" t="inlineStr">
+        <is>
+          <t>-36.570021049278914,174.69499148990542</t>
+        </is>
+      </c>
+      <c r="O599" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>-36.56190647906891,174.6973800449286</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>-36.56271775432849,174.69760578600037</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>-36.56323760228638,174.69667465834806</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr">
+        <is>
+          <t>-36.56388348267507,174.69621576985904</t>
+        </is>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>-36.564528819380165,174.695795042556</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>-36.565185421558674,174.6954523293126</t>
+        </is>
+      </c>
+      <c r="H600" t="inlineStr">
+        <is>
+          <t>-36.565868190753214,174.69523701886345</t>
+        </is>
+      </c>
+      <c r="I600" t="inlineStr">
+        <is>
+          <t>-36.56654485500974,174.6949428099986</t>
+        </is>
+      </c>
+      <c r="J600" t="inlineStr">
+        <is>
+          <t>-36.56724385429332,174.69488578626093</t>
+        </is>
+      </c>
+      <c r="K600" t="inlineStr">
+        <is>
+          <t>-36.56794365191832,174.6948200231795</t>
+        </is>
+      </c>
+      <c r="L600" t="inlineStr">
+        <is>
+          <t>-36.56865416064833,174.69485763217997</t>
+        </is>
+      </c>
+      <c r="M600" t="inlineStr">
+        <is>
+          <t>-36.56934179116271,174.69484072929404</t>
+        </is>
+      </c>
+      <c r="N600" t="inlineStr">
+        <is>
+          <t>-36.570019902058775,174.69499769778633</t>
+        </is>
+      </c>
+      <c r="O600" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0137/nzd0137.xlsx
+++ b/data/nzd0137/nzd0137.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O600"/>
+  <dimension ref="A1:O602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30918,7 +30918,7 @@
         <v>402.19</v>
       </c>
       <c r="C600" t="n">
-        <v>448.26</v>
+        <v>452.58</v>
       </c>
       <c r="D600" t="n">
         <v>388.52</v>
@@ -30954,6 +30954,108 @@
         <v>385.53</v>
       </c>
       <c r="O600" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="n">
+        <v>402.19</v>
+      </c>
+      <c r="C601" t="n">
+        <v>447.17</v>
+      </c>
+      <c r="D601" t="n">
+        <v>386.88</v>
+      </c>
+      <c r="E601" t="n">
+        <v>369.6</v>
+      </c>
+      <c r="F601" t="n">
+        <v>366.94</v>
+      </c>
+      <c r="G601" t="n">
+        <v>374.53</v>
+      </c>
+      <c r="H601" t="n">
+        <v>378.68</v>
+      </c>
+      <c r="I601" t="n">
+        <v>374.93</v>
+      </c>
+      <c r="J601" t="n">
+        <v>387.02</v>
+      </c>
+      <c r="K601" t="n">
+        <v>384.58</v>
+      </c>
+      <c r="L601" t="n">
+        <v>391.92</v>
+      </c>
+      <c r="M601" t="n">
+        <v>388.03</v>
+      </c>
+      <c r="N601" t="n">
+        <v>386.81</v>
+      </c>
+      <c r="O601" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="n">
+        <v>395.68</v>
+      </c>
+      <c r="C602" t="n">
+        <v>449.19</v>
+      </c>
+      <c r="D602" t="n">
+        <v>386.88</v>
+      </c>
+      <c r="E602" t="n">
+        <v>369.69</v>
+      </c>
+      <c r="F602" t="n">
+        <v>366.77</v>
+      </c>
+      <c r="G602" t="n">
+        <v>373.87</v>
+      </c>
+      <c r="H602" t="n">
+        <v>378.03</v>
+      </c>
+      <c r="I602" t="n">
+        <v>374.68</v>
+      </c>
+      <c r="J602" t="n">
+        <v>386.79</v>
+      </c>
+      <c r="K602" t="n">
+        <v>384.69</v>
+      </c>
+      <c r="L602" t="n">
+        <v>391.97</v>
+      </c>
+      <c r="M602" t="n">
+        <v>388.19</v>
+      </c>
+      <c r="N602" t="n">
+        <v>387.17</v>
+      </c>
+      <c r="O602" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -30970,7 +31072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B612"/>
+  <dimension ref="A1:B614"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37093,6 +37195,26 @@
       </c>
       <c r="B612" t="n">
         <v>-0.83</v>
+      </c>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B613" t="n">
+        <v>1.05</v>
+      </c>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B614" t="n">
+        <v>-0.86</v>
       </c>
     </row>
   </sheetData>
@@ -37261,28 +37383,28 @@
         <v>0.0117</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2320716926471649</v>
+        <v>-0.2745425930964801</v>
       </c>
       <c r="J2" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K2" t="n">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="L2" t="n">
-        <v>0.004500390512752972</v>
+        <v>0.006214515457419134</v>
       </c>
       <c r="M2" t="n">
-        <v>19.19938449759849</v>
+        <v>19.31026733127767</v>
       </c>
       <c r="N2" t="n">
-        <v>618.5421182501509</v>
+        <v>628.5236552168542</v>
       </c>
       <c r="O2" t="n">
-        <v>24.87050699624258</v>
+        <v>25.07037405418703</v>
       </c>
       <c r="P2" t="n">
-        <v>464.8700880039025</v>
+        <v>465.3492066196508</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37339,28 +37461,28 @@
         <v>0.0101</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.08602037024668494</v>
+        <v>-0.08920300393781587</v>
       </c>
       <c r="J3" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K3" t="n">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="L3" t="n">
-        <v>0.001428630798985475</v>
+        <v>0.001547688149851512</v>
       </c>
       <c r="M3" t="n">
-        <v>12.7968359618687</v>
+        <v>12.76691399796283</v>
       </c>
       <c r="N3" t="n">
-        <v>266.9870365208799</v>
+        <v>266.1806095025303</v>
       </c>
       <c r="O3" t="n">
-        <v>16.33973795753408</v>
+        <v>16.31504243030125</v>
       </c>
       <c r="P3" t="n">
-        <v>457.1345656674033</v>
+        <v>457.1703434054185</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37417,28 +37539,28 @@
         <v>0.0257</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.06688580333940207</v>
+        <v>-0.07361296248008294</v>
       </c>
       <c r="J4" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K4" t="n">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="L4" t="n">
-        <v>0.002658762954492633</v>
+        <v>0.003232656539039258</v>
       </c>
       <c r="M4" t="n">
-        <v>6.989815648815706</v>
+        <v>6.997097997556803</v>
       </c>
       <c r="N4" t="n">
-        <v>86.90364849761622</v>
+        <v>86.91175079638913</v>
       </c>
       <c r="O4" t="n">
-        <v>9.322212639583814</v>
+        <v>9.322647198966028</v>
       </c>
       <c r="P4" t="n">
-        <v>398.1856866407542</v>
+        <v>398.261203292723</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -37495,28 +37617,28 @@
         <v>0.0308</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.04912978333033163</v>
+        <v>-0.05561320046229593</v>
       </c>
       <c r="J5" t="n">
+        <v>601</v>
+      </c>
+      <c r="K5" t="n">
         <v>599</v>
       </c>
-      <c r="K5" t="n">
-        <v>597</v>
-      </c>
       <c r="L5" t="n">
-        <v>0.002820505993931022</v>
+        <v>0.003616363769091469</v>
       </c>
       <c r="M5" t="n">
-        <v>4.816591264268036</v>
+        <v>4.836480597332264</v>
       </c>
       <c r="N5" t="n">
-        <v>44.64785143937664</v>
+        <v>44.78168152652987</v>
       </c>
       <c r="O5" t="n">
-        <v>6.68190477628772</v>
+        <v>6.691911649635691</v>
       </c>
       <c r="P5" t="n">
-        <v>380.2246985833642</v>
+        <v>380.2969021795359</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -37573,28 +37695,28 @@
         <v>0.0327</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1332567441184439</v>
+        <v>-0.1395826622124193</v>
       </c>
       <c r="J6" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K6" t="n">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L6" t="n">
-        <v>0.03901990789624399</v>
+        <v>0.04249269085862017</v>
       </c>
       <c r="M6" t="n">
-        <v>3.635446821525132</v>
+        <v>3.654430788628661</v>
       </c>
       <c r="N6" t="n">
-        <v>22.66691964696918</v>
+        <v>22.85701978445535</v>
       </c>
       <c r="O6" t="n">
-        <v>4.760978853867047</v>
+        <v>4.780901566070499</v>
       </c>
       <c r="P6" t="n">
-        <v>379.4179289475015</v>
+        <v>379.4887257145575</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -37651,28 +37773,28 @@
         <v>0.0372</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.04004624807289712</v>
+        <v>-0.04418346552154211</v>
       </c>
       <c r="J7" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K7" t="n">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L7" t="n">
-        <v>0.004485838591188784</v>
+        <v>0.005464135781099166</v>
       </c>
       <c r="M7" t="n">
-        <v>3.347543948856894</v>
+        <v>3.359385454551447</v>
       </c>
       <c r="N7" t="n">
-        <v>18.44647657368543</v>
+        <v>18.49895965229756</v>
       </c>
       <c r="O7" t="n">
-        <v>4.294936154785706</v>
+        <v>4.301041693857147</v>
       </c>
       <c r="P7" t="n">
-        <v>381.1512711385392</v>
+        <v>381.1975740071518</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -37729,28 +37851,28 @@
         <v>0.0354</v>
       </c>
       <c r="I8" t="n">
-        <v>0.02415745640880598</v>
+        <v>0.02414933560666114</v>
       </c>
       <c r="J8" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K8" t="n">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002772742440088516</v>
+        <v>0.00279246528388355</v>
       </c>
       <c r="M8" t="n">
-        <v>2.493613413411707</v>
+        <v>2.486375229164696</v>
       </c>
       <c r="N8" t="n">
-        <v>10.87859925106157</v>
+        <v>10.84268718260319</v>
       </c>
       <c r="O8" t="n">
-        <v>3.298272161459932</v>
+        <v>3.292823588138787</v>
       </c>
       <c r="P8" t="n">
-        <v>377.7155914420678</v>
+        <v>377.7156835341963</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -37807,28 +37929,28 @@
         <v>0.0516</v>
       </c>
       <c r="I9" t="n">
-        <v>0.07309353959113049</v>
+        <v>0.06969030460411024</v>
       </c>
       <c r="J9" t="n">
+        <v>601</v>
+      </c>
+      <c r="K9" t="n">
         <v>599</v>
       </c>
-      <c r="K9" t="n">
-        <v>597</v>
-      </c>
       <c r="L9" t="n">
-        <v>0.02863525097259734</v>
+        <v>0.02608909563027861</v>
       </c>
       <c r="M9" t="n">
-        <v>2.2983374671394</v>
+        <v>2.306196468519795</v>
       </c>
       <c r="N9" t="n">
-        <v>9.406025074098382</v>
+        <v>9.451700310779986</v>
       </c>
       <c r="O9" t="n">
-        <v>3.066924367195641</v>
+        <v>3.074361772918078</v>
       </c>
       <c r="P9" t="n">
-        <v>377.6654598670762</v>
+        <v>377.7035367842952</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -37885,28 +38007,28 @@
         <v>0.0608</v>
       </c>
       <c r="I10" t="n">
-        <v>0.008468473378803772</v>
+        <v>0.008183517179178234</v>
       </c>
       <c r="J10" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K10" t="n">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0004162874045924303</v>
+        <v>0.0003917703149837193</v>
       </c>
       <c r="M10" t="n">
-        <v>2.228197734847846</v>
+        <v>2.221971440970115</v>
       </c>
       <c r="N10" t="n">
-        <v>8.96152446938587</v>
+        <v>8.9320887726525</v>
       </c>
       <c r="O10" t="n">
-        <v>2.993580543326982</v>
+        <v>2.988660029620716</v>
       </c>
       <c r="P10" t="n">
-        <v>387.0768750319695</v>
+        <v>387.0800617253518</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -37963,28 +38085,28 @@
         <v>0.0586</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.01395883777966065</v>
+        <v>-0.01648864365465282</v>
       </c>
       <c r="J11" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K11" t="n">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0009288673828755645</v>
+        <v>0.001300604330254473</v>
       </c>
       <c r="M11" t="n">
-        <v>2.458482011914233</v>
+        <v>2.459985201924422</v>
       </c>
       <c r="N11" t="n">
-        <v>10.90653907214113</v>
+        <v>10.91274966470166</v>
       </c>
       <c r="O11" t="n">
-        <v>3.302504969283337</v>
+        <v>3.303445120582702</v>
       </c>
       <c r="P11" t="n">
-        <v>388.6005991050136</v>
+        <v>388.6288861393794</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -38041,28 +38163,28 @@
         <v>0.06809999999999999</v>
       </c>
       <c r="I12" t="n">
-        <v>0.008104925571688624</v>
+        <v>0.006530107889393767</v>
       </c>
       <c r="J12" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K12" t="n">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0002902265349932209</v>
+        <v>0.0001896257564216741</v>
       </c>
       <c r="M12" t="n">
-        <v>2.557157319577902</v>
+        <v>2.5551600906715</v>
       </c>
       <c r="N12" t="n">
-        <v>11.77553437746877</v>
+        <v>11.75264890963344</v>
       </c>
       <c r="O12" t="n">
-        <v>3.431549850646027</v>
+        <v>3.428213661607665</v>
       </c>
       <c r="P12" t="n">
-        <v>393.9616770682803</v>
+        <v>393.9792859343331</v>
       </c>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
@@ -38119,28 +38241,28 @@
         <v>0.08550000000000001</v>
       </c>
       <c r="I13" t="n">
-        <v>0.06473928757920754</v>
+        <v>0.06252671337214878</v>
       </c>
       <c r="J13" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K13" t="n">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="L13" t="n">
-        <v>0.01820469272560932</v>
+        <v>0.01708669066930135</v>
       </c>
       <c r="M13" t="n">
-        <v>2.47406977342964</v>
+        <v>2.475470208881536</v>
       </c>
       <c r="N13" t="n">
-        <v>11.71546117962515</v>
+        <v>11.70893099738893</v>
       </c>
       <c r="O13" t="n">
-        <v>3.422785587737735</v>
+        <v>3.421831526739581</v>
       </c>
       <c r="P13" t="n">
-        <v>389.5075190531298</v>
+        <v>389.5322807527263</v>
       </c>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
@@ -38197,28 +38319,28 @@
         <v>0.1502</v>
       </c>
       <c r="I14" t="n">
-        <v>0.0358253042362776</v>
+        <v>0.03602025702927047</v>
       </c>
       <c r="J14" t="n">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="K14" t="n">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="L14" t="n">
-        <v>0.005692799235296642</v>
+        <v>0.005799230157136792</v>
       </c>
       <c r="M14" t="n">
-        <v>2.694439279184912</v>
+        <v>2.686455422973627</v>
       </c>
       <c r="N14" t="n">
-        <v>11.60728852792823</v>
+        <v>11.56882986355752</v>
       </c>
       <c r="O14" t="n">
-        <v>3.406947097905724</v>
+        <v>3.401298261481565</v>
       </c>
       <c r="P14" t="n">
-        <v>385.750328656923</v>
+        <v>385.7481421864378</v>
       </c>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
@@ -38256,7 +38378,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O600"/>
+  <dimension ref="A1:O602"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84199,7 +84321,7 @@
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>-36.56271775432849,174.69760578600037</t>
+          <t>-36.56272947425599,174.6976518110478</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
@@ -84258,6 +84380,160 @@
         </is>
       </c>
       <c r="O600" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-17 22:11:11+00:00</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>-36.56190647906891,174.6973800449286</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>-36.56271479721429,174.69759417320114</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>-36.56323313642964,174.69665719227373</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>-36.56387954201267,174.69620316485114</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>-36.5645211510096,174.69577593761284</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>-36.56517981908623,174.69543513247189</t>
+        </is>
+      </c>
+      <c r="H601" t="inlineStr">
+        <is>
+          <t>-36.565863397983364,174.6952160581135</t>
+        </is>
+      </c>
+      <c r="I601" t="inlineStr">
+        <is>
+          <t>-36.566543446874284,174.69493541583304</t>
+        </is>
+      </c>
+      <c r="J601" t="inlineStr">
+        <is>
+          <t>-36.567243405190005,174.69488112683277</t>
+        </is>
+      </c>
+      <c r="K601" t="inlineStr">
+        <is>
+          <t>-36.56794345492128,174.69481310029133</t>
+        </is>
+      </c>
+      <c r="L601" t="inlineStr">
+        <is>
+          <t>-36.56865419207853,174.6948529396832</t>
+        </is>
+      </c>
+      <c r="M601" t="inlineStr">
+        <is>
+          <t>-36.56934162993656,174.69484216797838</t>
+        </is>
+      </c>
+      <c r="N601" t="inlineStr">
+        <is>
+          <t>-36.57001732584397,174.6950116382901</t>
+        </is>
+      </c>
+      <c r="O601" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-26 22:05:06+00:00</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>-36.56188974822671,174.697310334885</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>-36.562720277369976,174.69761569416917</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>-36.56323313642964,174.69665719227373</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr">
+        <is>
+          <t>-36.563879835119835,174.69620410241367</t>
+        </is>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>-36.56452046848432,174.69577423717303</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>-36.56517759159647,174.69542829517445</t>
+        </is>
+      </c>
+      <c r="H602" t="inlineStr">
+        <is>
+          <t>-36.56586180039257,174.69520907119735</t>
+        </is>
+      </c>
+      <c r="I602" t="inlineStr">
+        <is>
+          <t>-36.5665429291773,174.69493269738987</t>
+        </is>
+      </c>
+      <c r="J602" t="inlineStr">
+        <is>
+          <t>-36.5672431592524,174.69487857524118</t>
+        </is>
+      </c>
+      <c r="K602" t="inlineStr">
+        <is>
+          <t>-36.56794348987239,174.69481432854568</t>
+        </is>
+      </c>
+      <c r="L602" t="inlineStr">
+        <is>
+          <t>-36.568654188336865,174.69485349831373</t>
+        </is>
+      </c>
+      <c r="M602" t="inlineStr">
+        <is>
+          <t>-36.56934143150436,174.69484393866682</t>
+        </is>
+      </c>
+      <c r="N602" t="inlineStr">
+        <is>
+          <t>-36.570016601283264,174.69501555905663</t>
+        </is>
+      </c>
+      <c r="O602" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
